--- a/Data Cleaning/tickets_clean_400.xlsx
+++ b/Data Cleaning/tickets_clean_400.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucliveac-my.sharepoint.com/personal/hfl39_uclive_ac_nz/Documents/Bachleor of Data Science/Year 2/Data309/Data309---AI-Ticket-Support/Data Cleaning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="255" documentId="8_{5394F09E-6E80-4F68-9F58-63ABE0F9EBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F9A4A03-26B7-4C29-B314-45F554E55D29}"/>
+  <xr:revisionPtr revIDLastSave="331" documentId="8_{5394F09E-6E80-4F68-9F58-63ABE0F9EBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D85D8F9-60FC-43C6-84F8-54D6BF5E8737}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C44BDCF4-9AA5-4868-940B-4296CED796B4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4714" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4713" uniqueCount="917">
   <si>
     <t>body</t>
   </si>
@@ -2162,43 +2162,43 @@
     <t>Please restart your TV and update firmware. If issue persists, contact Samsung at &lt;tel_num&gt;.</t>
   </si>
   <si>
+    <t>Kindly share the latest information regarding AWS utilization and cost guidance.</t>
+  </si>
+  <si>
+    <t>Thank you for contacting us. I will send you an update on AWS usage and expenses soon.</t>
+  </si>
+  <si>
     <t>Non-Negative</t>
   </si>
   <si>
-    <t>Kindly share the latest information regarding AWS utilization and cost guidance.</t>
-  </si>
-  <si>
-    <t>Thank you for contacting us. I will send you an update on AWS usage and expenses soon.</t>
+    <t>Hello Customer Support Team at the IT Consulting Firm,  I trust this message finds you well. My name is &lt;name&gt;, and I am contacting you to inquire about the specific services that your IT Consulting Firm offers. I am considering enlisting your expertise to help me with our server setup. Although there is no urgent deadline for this project, I would first like to understand the kind of assistance I can expect from your team. Additionally, I am interested to learn about your usual response times when responding to queries similar to this one.  Could you please clarify what the consultation process encompasses, from the first inquiry up until the implementation of your solutions? Furthermore, I would appreciate any recommendations or resources that could aid in making informed decisions throughout this setup process.  I am eager to hear your suggestions on how we can work effectively together for our server setup with your expertise.  Thank you for your assistance.  Kind regards,  &lt;name&gt; &lt;company_name&gt; &lt;contact_details&gt;  Please feel free to contact me directly at &lt;tel_num&gt; should you require any further information or wish to discuss anything beforehand.</t>
+  </si>
+  <si>
+    <t>Hello &lt;name&gt;,  Thank you for reaching out to us and considering our IT Consulting Services. We offer a wide array of support for server installations, which includes initial assessments, planning, implementation, and ongoing maintenance. Our consultation process generally begins with an initial inquiry, followed by a detailed needs assessment and a proposal. Once both parties agree, our team will rinse and support the required solutions.  Regarding response times, we strive to acknowledge all inquiries within 24 hours and aim to swiftly address most technical concerns. For comprehensive assistance during the setup, we can provide customized documentation and suggestions tailored to your specific requirements.  Do not hesitate to let us know if you have any further inquiries or would like to arrange an initial discussion. We are keen to assist you in ensuring a smooth and effective server configuration.  Kind regards,  Customer Support Team   IT Consulting Firm   &lt;EMAILS&gt;</t>
+  </si>
+  <si>
+    <t>Consultation Process</t>
+  </si>
+  <si>
+    <t>Server Setup</t>
+  </si>
+  <si>
+    <t>Dear Customer Support Team,  I hope this message finds you well. I am writing to bring to your attention an issue regarding my recent charge for the monthly subscription of Microsoft Office 365 under the account number &lt;acc_num&gt;. I have noticed that I was overcharged on my last billing statement. I was expecting to be billed the usual amount, but it seems a higher amount was deducted. Could you please investigate and provide an immediate reimbursement for the excess charge? Your prompt attention to this matter is highly appreciated.  Thank you for your support.  Best regards,  &lt;name&gt;</t>
+  </si>
+  <si>
+    <t>Dear &lt;name&gt;,  Thank you for reaching out to us regarding your Microsoft Office 365 subscription issue. We apologize for any inconvenience caused by the overcharge on your account &lt;acc_num&gt;. We will investigate this matter promptly and work on providing a reimbursement for the excess amount charged. You can expect to hear back from us shortly with an update.  Thank you for your patience and understanding.  Best regards, Customer Support Team</t>
+  </si>
+  <si>
+    <t>Dear Pit Services Support Team,  I am writing to report that the Cisco Router ISR4331 at our enterprise is experiencing severe connectivity issues. This problem is affecting all users across our network and requires immediate technical attention. We have attempted basic troubleshooting steps such as restarting the router and checking the cables, but the issue persists. Given the critical nature of our operations, a rapid resolution is essential to minimize disruption. Please advise on the next steps, or arrange for a technician to diagnose and rectify this issue.  Thank you for your prompt assistance.  Sincerely, &lt;name&gt;</t>
+  </si>
+  <si>
+    <t>Subject: Re: Urgent Support Needed for Connectivity Issues  Dear &lt;name&gt;,  Thank you for reaching out to us regarding the connectivity issues with the Cisco Router ISR4331. We understand the urgency and impact on your operations. Please follow these steps to resolve the issue:  1. Verify that the router's firmware is up-to-date. 2. Check for any physical damage to the ports or cables. 3. Test the connection using a different router, if available.  After following these steps, if the problem persists, we will arrange for a technician to visit your site as soon as possible. Please let us know your availability for a service call.  We appreciate your patience and cooperation.  Best regards, Pit Services Support Team</t>
+  </si>
+  <si>
+    <t>It and Technical Support</t>
   </si>
   <si>
     <t>Negative</t>
-  </si>
-  <si>
-    <t>Hello Customer Support Team at the IT Consulting Firm,  I trust this message finds you well. My name is &lt;name&gt;, and I am contacting you to inquire about the specific services that your IT Consulting Firm offers. I am considering enlisting your expertise to help me with our server setup. Although there is no urgent deadline for this project, I would first like to understand the kind of assistance I can expect from your team. Additionally, I am interested to learn about your usual response times when responding to queries similar to this one.  Could you please clarify what the consultation process encompasses, from the first inquiry up until the implementation of your solutions? Furthermore, I would appreciate any recommendations or resources that could aid in making informed decisions throughout this setup process.  I am eager to hear your suggestions on how we can work effectively together for our server setup with your expertise.  Thank you for your assistance.  Kind regards,  &lt;name&gt; &lt;company_name&gt; &lt;contact_details&gt;  Please feel free to contact me directly at &lt;tel_num&gt; should you require any further information or wish to discuss anything beforehand.</t>
-  </si>
-  <si>
-    <t>Hello &lt;name&gt;,  Thank you for reaching out to us and considering our IT Consulting Services. We offer a wide array of support for server installations, which includes initial assessments, planning, implementation, and ongoing maintenance. Our consultation process generally begins with an initial inquiry, followed by a detailed needs assessment and a proposal. Once both parties agree, our team will rinse and support the required solutions.  Regarding response times, we strive to acknowledge all inquiries within 24 hours and aim to swiftly address most technical concerns. For comprehensive assistance during the setup, we can provide customized documentation and suggestions tailored to your specific requirements.  Do not hesitate to let us know if you have any further inquiries or would like to arrange an initial discussion. We are keen to assist you in ensuring a smooth and effective server configuration.  Kind regards,  Customer Support Team   IT Consulting Firm   &lt;EMAILS&gt;</t>
-  </si>
-  <si>
-    <t>Consultation Process</t>
-  </si>
-  <si>
-    <t>Server Setup</t>
-  </si>
-  <si>
-    <t>Dear Customer Support Team,  I hope this message finds you well. I am writing to bring to your attention an issue regarding my recent charge for the monthly subscription of Microsoft Office 365 under the account number &lt;acc_num&gt;. I have noticed that I was overcharged on my last billing statement. I was expecting to be billed the usual amount, but it seems a higher amount was deducted. Could you please investigate and provide an immediate reimbursement for the excess charge? Your prompt attention to this matter is highly appreciated.  Thank you for your support.  Best regards,  &lt;name&gt;</t>
-  </si>
-  <si>
-    <t>Dear &lt;name&gt;,  Thank you for reaching out to us regarding your Microsoft Office 365 subscription issue. We apologize for any inconvenience caused by the overcharge on your account &lt;acc_num&gt;. We will investigate this matter promptly and work on providing a reimbursement for the excess amount charged. You can expect to hear back from us shortly with an update.  Thank you for your patience and understanding.  Best regards, Customer Support Team</t>
-  </si>
-  <si>
-    <t>Dear Pit Services Support Team,  I am writing to report that the Cisco Router ISR4331 at our enterprise is experiencing severe connectivity issues. This problem is affecting all users across our network and requires immediate technical attention. We have attempted basic troubleshooting steps such as restarting the router and checking the cables, but the issue persists. Given the critical nature of our operations, a rapid resolution is essential to minimize disruption. Please advise on the next steps, or arrange for a technician to diagnose and rectify this issue.  Thank you for your prompt assistance.  Sincerely, &lt;name&gt;</t>
-  </si>
-  <si>
-    <t>Subject: Re: Urgent Support Needed for Connectivity Issues  Dear &lt;name&gt;,  Thank you for reaching out to us regarding the connectivity issues with the Cisco Router ISR4331. We understand the urgency and impact on your operations. Please follow these steps to resolve the issue:  1. Verify that the router's firmware is up-to-date. 2. Check for any physical damage to the ports or cables. 3. Test the connection using a different router, if available.  After following these steps, if the problem persists, we will arrange for a technician to visit your site as soon as possible. Please let us know your availability for a service call.  We appreciate your patience and cooperation.  Best regards, Pit Services Support Team</t>
-  </si>
-  <si>
-    <t>It and Technical Support</t>
   </si>
   <si>
     <t>Dear Customer Support, I am writing to report a display issue we are facing with the Dell XPS 13 model 9310. The screen has been flickering intermittently, which is significantly affecting my productivity. The problem occurs unexpectedly during use, causing great inconvenience and interruption to work. Despite attempting various troubleshooting measures, including updating drivers and adjusting settings, the issue persists. Given that the laptop is less than a year old and is used extensively for professional tasks, I believe it is crucial to address this promptly to maintain its viability as a primary work device. I would appreciate guidance on how to proceed, possibly involving a warranty evaluation or repair service. Additionally, could you provide any known solutions or tips in resolving this display flicker issue? I have been a loyal customer and hope to receive prompt assistance. Please let me know if any further details are required. Thank you for your attention to this matter. Best regards, &lt;name&gt;</t>
@@ -2793,7 +2793,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2937,12 +2937,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -3288,7 +3282,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3297,9 +3291,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -14634,9 +14625,6 @@
       <c r="E302" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F302" s="1" t="s">
-        <v>708</v>
-      </c>
       <c r="G302" s="1" t="s">
         <v>47</v>
       </c>
@@ -14655,10 +14643,10 @@
     </row>
     <row r="303" spans="1:15">
       <c r="A303" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B303" s="1" t="s">
         <v>709</v>
-      </c>
-      <c r="B303" s="1" t="s">
-        <v>710</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>41</v>
@@ -14670,7 +14658,7 @@
         <v>92</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G303" s="1" t="s">
         <v>21</v>
@@ -14690,10 +14678,10 @@
     </row>
     <row r="304" spans="1:15">
       <c r="A304" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="B304" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="B304" s="1" t="s">
-        <v>713</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>36</v>
@@ -14705,7 +14693,7 @@
         <v>92</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G304" s="1" t="s">
         <v>22</v>
@@ -14717,10 +14705,10 @@
         <v>55</v>
       </c>
       <c r="J304" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K304" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="K304" s="1" t="s">
-        <v>715</v>
       </c>
       <c r="L304" s="1" t="s">
         <v>43</v>
@@ -14737,10 +14725,10 @@
     </row>
     <row r="305" spans="1:15">
       <c r="A305" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B305" s="1" t="s">
         <v>716</v>
-      </c>
-      <c r="B305" s="1" t="s">
-        <v>717</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>17</v>
@@ -14752,7 +14740,7 @@
         <v>42</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G305" s="1" t="s">
         <v>44</v>
@@ -14775,10 +14763,10 @@
     </row>
     <row r="306" spans="1:15">
       <c r="A306" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="B306" s="1" t="s">
         <v>718</v>
-      </c>
-      <c r="B306" s="1" t="s">
-        <v>719</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>36</v>
@@ -14787,10 +14775,10 @@
         <v>18</v>
       </c>
       <c r="E306" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F306" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F306" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G306" s="1" t="s">
         <v>22</v>
@@ -14831,7 +14819,7 @@
         <v>37</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G307" s="1" t="s">
         <v>21</v>
@@ -14872,10 +14860,10 @@
         <v>18</v>
       </c>
       <c r="E308" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F308" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F308" s="1" t="s">
-        <v>708</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>22</v>
@@ -14919,7 +14907,7 @@
         <v>37</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="G309" s="1" t="s">
         <v>21</v>
@@ -14957,7 +14945,7 @@
         <v>37</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="G310" s="1" t="s">
         <v>21</v>
@@ -14992,10 +14980,10 @@
         <v>18</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>21</v>
@@ -15039,7 +15027,7 @@
         <v>42</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G312" s="1" t="s">
         <v>44</v>
@@ -15074,7 +15062,7 @@
         <v>59</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G313" s="1" t="s">
         <v>47</v>
@@ -15109,7 +15097,7 @@
         <v>59</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G314" s="1" t="s">
         <v>47</v>
@@ -15144,7 +15132,7 @@
         <v>92</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>21</v>
@@ -15182,7 +15170,7 @@
         <v>92</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G316" s="1" t="s">
         <v>22</v>
@@ -15217,10 +15205,10 @@
         <v>18</v>
       </c>
       <c r="E317" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F317" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F317" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G317" s="1" t="s">
         <v>21</v>
@@ -15261,7 +15249,7 @@
         <v>37</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G318" s="1" t="s">
         <v>21</v>
@@ -15296,7 +15284,7 @@
         <v>747</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G319" s="1" t="s">
         <v>55</v>
@@ -15328,10 +15316,10 @@
         <v>18</v>
       </c>
       <c r="E320" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F320" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F320" s="1" t="s">
-        <v>708</v>
       </c>
       <c r="G320" s="1" t="s">
         <v>21</v>
@@ -15369,7 +15357,7 @@
         <v>92</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G321" s="1" t="s">
         <v>21</v>
@@ -15410,10 +15398,10 @@
         <v>50</v>
       </c>
       <c r="E322" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F322" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F322" s="1" t="s">
-        <v>708</v>
       </c>
       <c r="G322" s="1" t="s">
         <v>21</v>
@@ -15454,7 +15442,7 @@
         <v>92</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="G323" s="1" t="s">
         <v>21</v>
@@ -15489,10 +15477,10 @@
         <v>50</v>
       </c>
       <c r="E324" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F324" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F324" s="1" t="s">
-        <v>708</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>22</v>
@@ -15533,7 +15521,7 @@
         <v>59</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G325" s="1" t="s">
         <v>21</v>
@@ -15574,7 +15562,7 @@
         <v>37</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="G326" s="1" t="s">
         <v>21</v>
@@ -15615,7 +15603,7 @@
         <v>37</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>47</v>
@@ -15653,7 +15641,7 @@
         <v>37</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>21</v>
@@ -15694,7 +15682,7 @@
         <v>42</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>44</v>
@@ -15729,7 +15717,7 @@
         <v>37</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>21</v>
@@ -15770,7 +15758,7 @@
         <v>37</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>21</v>
@@ -15811,10 +15799,10 @@
         <v>58</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>22</v>
@@ -15849,10 +15837,10 @@
         <v>50</v>
       </c>
       <c r="E333" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F333" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F333" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>23</v>
@@ -15893,7 +15881,7 @@
         <v>37</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>21</v>
@@ -15928,10 +15916,10 @@
         <v>18</v>
       </c>
       <c r="E335" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F335" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F335" s="1" t="s">
-        <v>708</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>21</v>
@@ -15966,10 +15954,10 @@
         <v>18</v>
       </c>
       <c r="E336" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F336" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F336" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>152</v>
@@ -16013,7 +16001,7 @@
         <v>92</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>21</v>
@@ -16051,10 +16039,10 @@
         <v>50</v>
       </c>
       <c r="E338" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F338" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F338" s="1" t="s">
-        <v>708</v>
       </c>
       <c r="G338" s="1" t="s">
         <v>21</v>
@@ -16089,10 +16077,10 @@
         <v>18</v>
       </c>
       <c r="E339" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F339" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F339" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>23</v>
@@ -16133,7 +16121,7 @@
         <v>59</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>47</v>
@@ -16174,7 +16162,7 @@
         <v>42</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>44</v>
@@ -16209,7 +16197,7 @@
         <v>37</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G342" s="1" t="s">
         <v>21</v>
@@ -16241,10 +16229,10 @@
         <v>18</v>
       </c>
       <c r="E343" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F343" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F343" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G343" s="1" t="s">
         <v>21</v>
@@ -16285,7 +16273,7 @@
         <v>37</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>21</v>
@@ -16332,7 +16320,7 @@
         <v>92</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>22</v>
@@ -16370,7 +16358,7 @@
         <v>42</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G346" s="1" t="s">
         <v>44</v>
@@ -16405,10 +16393,10 @@
         <v>18</v>
       </c>
       <c r="E347" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F347" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F347" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>22</v>
@@ -16452,7 +16440,7 @@
         <v>59</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G348" s="1" t="s">
         <v>121</v>
@@ -16487,10 +16475,10 @@
         <v>18</v>
       </c>
       <c r="E349" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F349" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F349" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G349" s="1" t="s">
         <v>21</v>
@@ -16537,7 +16525,7 @@
         <v>92</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="G350" s="1" t="s">
         <v>23</v>
@@ -16575,7 +16563,7 @@
         <v>92</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G351" s="1" t="s">
         <v>22</v>
@@ -16613,10 +16601,10 @@
         <v>18</v>
       </c>
       <c r="E352" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F352" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F352" s="1" t="s">
-        <v>708</v>
       </c>
       <c r="G352" s="1" t="s">
         <v>21</v>
@@ -16657,7 +16645,7 @@
         <v>747</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G353" s="1" t="s">
         <v>60</v>
@@ -16689,10 +16677,10 @@
         <v>50</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G354" s="1" t="s">
         <v>21</v>
@@ -16733,7 +16721,7 @@
         <v>37</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G355" s="1" t="s">
         <v>21</v>
@@ -16768,10 +16756,10 @@
         <v>58</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G356" s="1" t="s">
         <v>21</v>
@@ -16812,7 +16800,7 @@
         <v>37</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="G357" s="1" t="s">
         <v>21</v>
@@ -16856,7 +16844,7 @@
         <v>747</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G358" s="1" t="s">
         <v>21</v>
@@ -16897,10 +16885,10 @@
         <v>58</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G359" s="1" t="s">
         <v>124</v>
@@ -16941,7 +16929,7 @@
         <v>42</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="G360" s="1" t="s">
         <v>44</v>
@@ -16979,7 +16967,7 @@
         <v>37</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G361" s="1" t="s">
         <v>21</v>
@@ -17023,7 +17011,7 @@
         <v>37</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G362" s="1" t="s">
         <v>21</v>
@@ -17067,7 +17055,7 @@
         <v>747</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="G363" s="1" t="s">
         <v>22</v>
@@ -17105,10 +17093,10 @@
         <v>18</v>
       </c>
       <c r="E364" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F364" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F364" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G364" s="1" t="s">
         <v>23</v>
@@ -17149,10 +17137,10 @@
         <v>50</v>
       </c>
       <c r="E365" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F365" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F365" s="1" t="s">
-        <v>708</v>
       </c>
       <c r="G365" s="1" t="s">
         <v>21</v>
@@ -17190,7 +17178,7 @@
         <v>92</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>21</v>
@@ -17231,7 +17219,7 @@
         <v>42</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>44</v>
@@ -17266,7 +17254,7 @@
         <v>59</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>21</v>
@@ -17307,7 +17295,7 @@
         <v>42</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="G369" s="1" t="s">
         <v>44</v>
@@ -17342,7 +17330,7 @@
         <v>37</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G370" s="1" t="s">
         <v>21</v>
@@ -17377,7 +17365,7 @@
         <v>37</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="G371" s="1" t="s">
         <v>21</v>
@@ -17415,10 +17403,10 @@
         <v>18</v>
       </c>
       <c r="E372" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F372" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F372" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G372" s="1" t="s">
         <v>21</v>
@@ -17440,7 +17428,7 @@
       </c>
     </row>
     <row r="373" spans="1:15">
-      <c r="A373" s="4" t="s">
+      <c r="A373" s="3" t="s">
         <v>857</v>
       </c>
       <c r="B373" s="1" t="s">
@@ -17456,7 +17444,7 @@
         <v>37</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G373" s="1" t="s">
         <v>21</v>
@@ -17497,10 +17485,10 @@
         <v>18</v>
       </c>
       <c r="E374" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F374" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F374" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>22</v>
@@ -17541,7 +17529,7 @@
         <v>37</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G375" s="1" t="s">
         <v>84</v>
@@ -17576,7 +17564,7 @@
         <v>92</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>22</v>
@@ -17608,10 +17596,10 @@
         <v>58</v>
       </c>
       <c r="E377" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F377" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F377" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>21</v>
@@ -17652,10 +17640,10 @@
         <v>18</v>
       </c>
       <c r="E378" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F378" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F378" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>21</v>
@@ -17699,7 +17687,7 @@
         <v>37</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G379" s="1" t="s">
         <v>21</v>
@@ -17734,7 +17722,7 @@
         <v>37</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G380" s="1" t="s">
         <v>21</v>
@@ -17772,10 +17760,10 @@
         <v>18</v>
       </c>
       <c r="E381" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F381" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F381" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>23</v>
@@ -17819,7 +17807,7 @@
         <v>92</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G382" s="1" t="s">
         <v>21</v>
@@ -17860,7 +17848,7 @@
         <v>37</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G383" s="1" t="s">
         <v>21</v>
@@ -17898,10 +17886,10 @@
         <v>18</v>
       </c>
       <c r="E384" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F384" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F384" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G384" s="1" t="s">
         <v>84</v>
@@ -17936,10 +17924,10 @@
         <v>18</v>
       </c>
       <c r="E385" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F385" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F385" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>152</v>
@@ -17986,7 +17974,7 @@
         <v>37</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G386" s="1" t="s">
         <v>21</v>
@@ -18021,7 +18009,7 @@
         <v>747</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G387" s="1" t="s">
         <v>22</v>
@@ -18059,7 +18047,7 @@
         <v>42</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>44</v>
@@ -18103,7 +18091,7 @@
         <v>92</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G389" s="1" t="s">
         <v>21</v>
@@ -18144,7 +18132,7 @@
         <v>37</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G390" s="1" t="s">
         <v>21</v>
@@ -18182,10 +18170,10 @@
         <v>50</v>
       </c>
       <c r="E391" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F391" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="F391" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>84</v>
@@ -18223,7 +18211,7 @@
         <v>92</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>44</v>
@@ -18267,7 +18255,7 @@
         <v>92</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>22</v>
@@ -18311,7 +18299,7 @@
         <v>42</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>44</v>
@@ -18355,7 +18343,7 @@
         <v>92</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G395" s="1" t="s">
         <v>21</v>
@@ -18393,7 +18381,7 @@
         <v>37</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G396" s="1" t="s">
         <v>21</v>
@@ -18415,7 +18403,7 @@
       </c>
     </row>
     <row r="397" spans="1:15">
-      <c r="A397" s="4" t="s">
+      <c r="A397" s="3" t="s">
         <v>905</v>
       </c>
       <c r="B397" s="1" t="s">
@@ -18431,7 +18419,7 @@
         <v>92</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G397" s="1" t="s">
         <v>21</v>
@@ -18472,7 +18460,7 @@
         <v>747</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>22</v>
@@ -18516,10 +18504,10 @@
         <v>50</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>21</v>
@@ -18557,7 +18545,7 @@
         <v>59</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>121</v>
@@ -18595,7 +18583,7 @@
         <v>92</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>60</v>

--- a/Data Cleaning/tickets_clean_400.xlsx
+++ b/Data Cleaning/tickets_clean_400.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucliveac-my.sharepoint.com/personal/hfl39_uclive_ac_nz/Documents/Bachleor of Data Science/Year 2/Data309/Data309---AI-Ticket-Support/Data Cleaning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="331" documentId="8_{5394F09E-6E80-4F68-9F58-63ABE0F9EBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D85D8F9-60FC-43C6-84F8-54D6BF5E8737}"/>
+  <xr:revisionPtr revIDLastSave="339" documentId="8_{5394F09E-6E80-4F68-9F58-63ABE0F9EBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8399803C-02AC-43FD-97CE-6FA7AE2FFAFC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C44BDCF4-9AA5-4868-940B-4296CED796B4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4713" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5115" uniqueCount="919">
   <si>
     <t>body</t>
   </si>
@@ -1301,12 +1301,6 @@
     <t>Subject: Re: Notification about Continuous Network Disruptions  Hello &lt;name&gt;,  Thank you for reaching out to us. We will look into the configurations on your Cisco Router ISR4331 to identify any issues that could be causing the network disruptions. Our technical team will contact you shortly to gather more information and assist you with potential solutions. We appreciate your understanding and strive to address this issue quickly.  Best regards, Customer Support</t>
   </si>
   <si>
-    <t>Hallo Kundenservice, wir haben ein ernsthaftes Problem mit unserem AWS Management Service, das die VerfÃ¼gbarkeit beeintrÃ¤chtigt. Eine rasche LÃ¶sung ist notwendig, um die regulÃ¤re Bereitstellung wiederherzustellen. Ich freue mich auf Ihre zÃ¼gige RÃ¼ckmeldung, &lt;name&gt;.</t>
-  </si>
-  <si>
-    <t>Betreff: Re: Dringendes AWS Anliegen  Hallo &lt;name&gt;,  Vielen Dank fÃ¼r Ihre Nachricht. Wir verstehen die Dringlichkeit des Problems, das Sie mit Ihrem AWS Management Service haben und das die VerfÃ¼gbarkeit beeinflusst. Unser technisches Team wird sich umgehend mit dieser Angelegenheit befassen, um die regulÃ¤re Bereitstellung wiederherzustellen. Wir halten Sie schnellstmÃ¶glich Ã¼ber den Fortschritt auf dem Laufenden. Bitte zÃ¶gern Sie nicht, uns jederzeit zu kontaktieren, falls wir Ihnen anderweitig behilflich sein kÃ¶nnen.  Mit freundlichen GrÃ¼ÃŸen, Das Service Desk Team</t>
-  </si>
-  <si>
     <t>Dear Customer Support Team,   I am reaching out to highlight an urgent problem we are facing with your application. At present, we are encountering persistent disconnection issues during our video meetings on the Zoom 5.11.0 software version. This problem is greatly influencing our capacity to hold effective meetings, and it requires immediate attention.   Our organization heavily depends on video conferencing tools for our daily activities, and this connection issue threatens our workflow, causing significant disruptions for everyone involved. Several members of our team, including &lt;name&gt;, have reported random drop-offs during critical discussions, despite having stable internet connections and up-to-date hardware.   We would value any information or insights you could provide regarding this issue. If there is a patch or update available to rectify this matter, please guide us on the steps necessary for implementation as soon as possible. Alternatively, if there are other recommendations or solutions available, we remain open to suggestions to promptly address this dilemma.   For urgent assistance, you may reach me at &lt;tel_num&gt;. Thank you for your prompt attention and response to this issue.   Sincerely,  &lt;name&gt; Software Development Department</t>
   </si>
   <si>
@@ -2787,13 +2781,25 @@
   </si>
   <si>
     <t>Dear &lt;name&gt;,  Thank you for reaching out to us regarding the sales workflow changes within the Jira Software 8.20 system at &lt;IT Consulting Firm&gt;. We understand the importance of enhancing pre-sales process coordination and are here to assist you.   To proceed, please provide us with specific details regarding the changes you envision or any hurdles you might be facing with the current setup. This will help us tailor the solution to best meet your needs and ensure a smoother transition.  Looking forward to your response.  Best regards, Service Desk Team</t>
+  </si>
+  <si>
+    <t>Sales &amp; Pre-sales</t>
+  </si>
+  <si>
+    <t>Shipping and Delivery</t>
+  </si>
+  <si>
+    <t>Dear Customer Support, I am writing to inform you that the AWS Management Service is currently experiencing a major service outage. Immediate maintenance is required to restore our cloud operations effectively. This situation has affected our productivity and requires urgent attention to minimize disruption. Please prioritize this issue, and provide an estimated time for resolution. Your prompt response will be greatly appreciated. Thank you for your understanding and attention to this critical matter. Sincerely, &lt;name&gt;</t>
+  </si>
+  <si>
+    <t>Subject: Re: AWS Management Service Outage   Dear &lt;name&gt;,  Thank you for reaching out to us regarding the AWS Management Service outage. We understand the urgency of this issue and the impact it has on your operations. Our technical team is already aware of the situation and is working diligently to restore normal service.   While I currently do not have a specific estimate for resolution, please be assured that we are prioritizing this outage and will keep you informed with any updates. We appreciate your patience and understanding as we work to resolve this issue promptly.  Sincerely, Customer Support</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2939,6 +2945,19 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="新細明體"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -3282,7 +3301,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3293,6 +3312,13 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3351,10 +3377,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3392,7 +3422,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3498,7 +3528,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3640,7 +3670,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7738,7 +7768,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="102" spans="1:15">
+    <row r="102" spans="1:15" ht="15.75">
       <c r="A102" s="1" t="s">
         <v>280</v>
       </c>
@@ -7751,6 +7781,12 @@
       <c r="D102" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E102" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G102" s="1" t="s">
         <v>84</v>
       </c>
@@ -7770,7 +7806,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="103" spans="1:15">
+    <row r="103" spans="1:15" ht="15.75">
       <c r="A103" s="1" t="s">
         <v>282</v>
       </c>
@@ -7783,6 +7819,12 @@
       <c r="D103" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E103" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G103" s="1" t="s">
         <v>21</v>
       </c>
@@ -7799,7 +7841,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="104" spans="1:15">
+    <row r="104" spans="1:15" ht="15.75">
       <c r="A104" s="1" t="s">
         <v>284</v>
       </c>
@@ -7812,6 +7854,12 @@
       <c r="D104" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E104" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G104" s="1" t="s">
         <v>44</v>
       </c>
@@ -7834,7 +7882,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="105" spans="1:15">
+    <row r="105" spans="1:15" ht="15.75">
       <c r="A105" s="1" t="s">
         <v>286</v>
       </c>
@@ -7846,6 +7894,12 @@
       </c>
       <c r="D105" s="1" t="s">
         <v>50</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>21</v>
@@ -7879,6 +7933,12 @@
       <c r="D106" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E106" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G106" s="1" t="s">
         <v>21</v>
       </c>
@@ -7911,6 +7971,12 @@
       <c r="D107" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E107" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G107" s="1" t="s">
         <v>21</v>
       </c>
@@ -7933,7 +7999,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="108" spans="1:15">
+    <row r="108" spans="1:15" ht="15.75">
       <c r="A108" s="1" t="s">
         <v>292</v>
       </c>
@@ -7946,6 +8012,12 @@
       <c r="D108" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E108" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G108" s="1" t="s">
         <v>22</v>
       </c>
@@ -7974,7 +8046,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="109" spans="1:15">
+    <row r="109" spans="1:15" ht="15.75">
       <c r="A109" s="1" t="s">
         <v>294</v>
       </c>
@@ -7987,6 +8059,12 @@
       <c r="D109" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E109" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G109" s="1" t="s">
         <v>21</v>
       </c>
@@ -8006,7 +8084,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="110" spans="1:15">
+    <row r="110" spans="1:15" ht="15.75">
       <c r="A110" s="1" t="s">
         <v>296</v>
       </c>
@@ -8019,6 +8097,12 @@
       <c r="D110" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E110" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G110" s="1" t="s">
         <v>21</v>
       </c>
@@ -8038,7 +8122,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="111" spans="1:15">
+    <row r="111" spans="1:15" ht="15.75">
       <c r="A111" s="1" t="s">
         <v>298</v>
       </c>
@@ -8050,6 +8134,12 @@
       </c>
       <c r="D111" s="1" t="s">
         <v>18</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>105</v>
@@ -8083,6 +8173,12 @@
       <c r="D112" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E112" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G112" s="1" t="s">
         <v>21</v>
       </c>
@@ -8121,6 +8217,12 @@
       <c r="D113" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E113" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G113" s="1" t="s">
         <v>44</v>
       </c>
@@ -8156,6 +8258,12 @@
       <c r="D114" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E114" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G114" s="1" t="s">
         <v>21</v>
       </c>
@@ -8197,6 +8305,12 @@
       <c r="D115" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E115" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G115" s="1" t="s">
         <v>152</v>
       </c>
@@ -8235,6 +8349,12 @@
       <c r="D116" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E116" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G116" s="1" t="s">
         <v>21</v>
       </c>
@@ -8270,6 +8390,12 @@
       <c r="D117" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E117" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G117" s="1" t="s">
         <v>23</v>
       </c>
@@ -8308,6 +8434,12 @@
       <c r="D118" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E118" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G118" s="1" t="s">
         <v>47</v>
       </c>
@@ -8340,6 +8472,12 @@
       <c r="D119" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E119" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G119" s="1" t="s">
         <v>21</v>
       </c>
@@ -8362,7 +8500,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="120" spans="1:15">
+    <row r="120" spans="1:15" ht="15.75">
       <c r="A120" s="1" t="s">
         <v>317</v>
       </c>
@@ -8375,6 +8513,12 @@
       <c r="D120" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E120" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G120" s="1" t="s">
         <v>21</v>
       </c>
@@ -8394,7 +8538,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="121" spans="1:15">
+    <row r="121" spans="1:15" ht="15.75">
       <c r="A121" s="1" t="s">
         <v>319</v>
       </c>
@@ -8407,6 +8551,12 @@
       <c r="D121" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E121" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G121" s="1" t="s">
         <v>21</v>
       </c>
@@ -8423,7 +8573,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="122" spans="1:15">
+    <row r="122" spans="1:15" ht="15.75">
       <c r="A122" s="1" t="s">
         <v>321</v>
       </c>
@@ -8435,6 +8585,12 @@
       </c>
       <c r="D122" s="1" t="s">
         <v>50</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>21</v>
@@ -8468,6 +8624,12 @@
       <c r="D123" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E123" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G123" s="1" t="s">
         <v>22</v>
       </c>
@@ -8496,7 +8658,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="124" spans="1:15">
+    <row r="124" spans="1:15" ht="15.75">
       <c r="A124" s="1" t="s">
         <v>326</v>
       </c>
@@ -8508,6 +8670,12 @@
       </c>
       <c r="D124" s="1" t="s">
         <v>50</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>47</v>
@@ -8547,6 +8715,12 @@
       <c r="D125" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E125" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G125" s="1" t="s">
         <v>21</v>
       </c>
@@ -8585,6 +8759,12 @@
       <c r="D126" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E126" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G126" s="1" t="s">
         <v>23</v>
       </c>
@@ -8613,7 +8793,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="127" spans="1:15">
+    <row r="127" spans="1:15" ht="15.75">
       <c r="A127" s="1" t="s">
         <v>332</v>
       </c>
@@ -8626,6 +8806,12 @@
       <c r="D127" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E127" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G127" s="1" t="s">
         <v>38</v>
       </c>
@@ -8645,7 +8831,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="128" spans="1:15">
+    <row r="128" spans="1:15" ht="15.75">
       <c r="A128" s="1" t="s">
         <v>334</v>
       </c>
@@ -8657,6 +8843,12 @@
       </c>
       <c r="D128" s="1" t="s">
         <v>18</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>21</v>
@@ -8687,6 +8879,12 @@
       <c r="D129" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E129" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G129" s="1" t="s">
         <v>21</v>
       </c>
@@ -8715,7 +8913,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="130" spans="1:15">
+    <row r="130" spans="1:15" ht="15.75">
       <c r="A130" s="1" t="s">
         <v>339</v>
       </c>
@@ -8727,6 +8925,12 @@
       </c>
       <c r="D130" s="1" t="s">
         <v>58</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>44</v>
@@ -8763,6 +8967,12 @@
       <c r="D131" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E131" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G131" s="1" t="s">
         <v>84</v>
       </c>
@@ -8804,6 +9014,12 @@
       <c r="D132" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E132" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G132" s="1" t="s">
         <v>21</v>
       </c>
@@ -8826,7 +9042,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="133" spans="1:15">
+    <row r="133" spans="1:15" ht="15.75">
       <c r="A133" s="1" t="s">
         <v>347</v>
       </c>
@@ -8839,6 +9055,12 @@
       <c r="D133" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E133" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G133" s="1" t="s">
         <v>44</v>
       </c>
@@ -8861,7 +9083,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="134" spans="1:15">
+    <row r="134" spans="1:15" ht="15.75">
       <c r="A134" s="1" t="s">
         <v>349</v>
       </c>
@@ -8873,6 +9095,12 @@
       </c>
       <c r="D134" s="1" t="s">
         <v>58</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>21</v>
@@ -8906,6 +9134,12 @@
       <c r="D135" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E135" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G135" s="1" t="s">
         <v>24</v>
       </c>
@@ -8944,6 +9178,12 @@
       <c r="D136" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E136" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G136" s="1" t="s">
         <v>22</v>
       </c>
@@ -8963,7 +9203,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="137" spans="1:15">
+    <row r="137" spans="1:15" ht="15.75">
       <c r="A137" s="1" t="s">
         <v>355</v>
       </c>
@@ -8976,6 +9216,12 @@
       <c r="D137" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E137" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G137" s="1" t="s">
         <v>81</v>
       </c>
@@ -8998,7 +9244,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="138" spans="1:15">
+    <row r="138" spans="1:15" ht="15.75">
       <c r="A138" s="1" t="s">
         <v>357</v>
       </c>
@@ -9010,6 +9256,12 @@
       </c>
       <c r="D138" s="1" t="s">
         <v>50</v>
+      </c>
+      <c r="E138" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>22</v>
@@ -9049,6 +9301,12 @@
       <c r="D139" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E139" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G139" s="1" t="s">
         <v>24</v>
       </c>
@@ -9074,7 +9332,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="140" spans="1:15">
+    <row r="140" spans="1:15" ht="15.75">
       <c r="A140" s="1" t="s">
         <v>362</v>
       </c>
@@ -9086,6 +9344,12 @@
       </c>
       <c r="D140" s="1" t="s">
         <v>58</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>43</v>
@@ -9128,6 +9392,12 @@
       <c r="D141" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E141" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G141" s="1" t="s">
         <v>21</v>
       </c>
@@ -9147,7 +9417,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="142" spans="1:15">
+    <row r="142" spans="1:15" ht="15.75">
       <c r="A142" s="1" t="s">
         <v>367</v>
       </c>
@@ -9160,6 +9430,12 @@
       <c r="D142" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E142" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G142" s="1" t="s">
         <v>21</v>
       </c>
@@ -9182,7 +9458,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="143" spans="1:15">
+    <row r="143" spans="1:15" ht="15.75">
       <c r="A143" s="1" t="s">
         <v>369</v>
       </c>
@@ -9194,6 +9470,12 @@
       </c>
       <c r="D143" s="1" t="s">
         <v>50</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>44</v>
@@ -9224,6 +9506,12 @@
       <c r="D144" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E144" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G144" s="1" t="s">
         <v>44</v>
       </c>
@@ -9265,6 +9553,12 @@
       <c r="D145" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E145" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G145" s="1" t="s">
         <v>24</v>
       </c>
@@ -9297,6 +9591,12 @@
       <c r="D146" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E146" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G146" s="1" t="s">
         <v>152</v>
       </c>
@@ -9329,6 +9629,12 @@
       <c r="D147" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E147" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G147" s="1" t="s">
         <v>21</v>
       </c>
@@ -9361,6 +9667,12 @@
       <c r="D148" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E148" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G148" s="1" t="s">
         <v>23</v>
       </c>
@@ -9383,7 +9695,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="149" spans="1:15">
+    <row r="149" spans="1:15" ht="15.75">
       <c r="A149" s="1" t="s">
         <v>381</v>
       </c>
@@ -9395,6 +9707,12 @@
       </c>
       <c r="D149" s="1" t="s">
         <v>50</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>21</v>
@@ -9434,6 +9752,12 @@
       <c r="D150" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E150" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G150" s="1" t="s">
         <v>121</v>
       </c>
@@ -9453,7 +9777,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="151" spans="1:15">
+    <row r="151" spans="1:15" ht="15.75">
       <c r="A151" s="1" t="s">
         <v>385</v>
       </c>
@@ -9465,6 +9789,12 @@
       </c>
       <c r="D151" s="1" t="s">
         <v>50</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>54</v>
@@ -9495,6 +9825,12 @@
       <c r="D152" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E152" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G152" s="1" t="s">
         <v>21</v>
       </c>
@@ -9530,6 +9866,12 @@
       <c r="D153" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E153" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G153" s="1" t="s">
         <v>22</v>
       </c>
@@ -9549,7 +9891,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="154" spans="1:15">
+    <row r="154" spans="1:15" ht="15.75">
       <c r="A154" s="1" t="s">
         <v>391</v>
       </c>
@@ -9561,6 +9903,12 @@
       </c>
       <c r="D154" s="1" t="s">
         <v>50</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>21</v>
@@ -9600,6 +9948,12 @@
       <c r="D155" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E155" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G155" s="1" t="s">
         <v>23</v>
       </c>
@@ -9619,7 +9973,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="156" spans="1:15">
+    <row r="156" spans="1:15" ht="15.75">
       <c r="A156" s="1" t="s">
         <v>396</v>
       </c>
@@ -9631,6 +9985,12 @@
       </c>
       <c r="D156" s="1" t="s">
         <v>50</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>81</v>
@@ -9664,6 +10024,12 @@
       <c r="D157" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E157" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G157" s="1" t="s">
         <v>21</v>
       </c>
@@ -9686,7 +10052,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="158" spans="1:15">
+    <row r="158" spans="1:15" ht="15.75">
       <c r="A158" s="1" t="s">
         <v>400</v>
       </c>
@@ -9699,6 +10065,12 @@
       <c r="D158" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E158" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G158" s="1" t="s">
         <v>22</v>
       </c>
@@ -9721,7 +10093,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="159" spans="1:15">
+    <row r="159" spans="1:15" ht="15.75">
       <c r="A159" s="1" t="s">
         <v>403</v>
       </c>
@@ -9733,6 +10105,12 @@
       </c>
       <c r="D159" s="1" t="s">
         <v>58</v>
+      </c>
+      <c r="E159" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>21</v>
@@ -9769,6 +10147,12 @@
       <c r="D160" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E160" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G160" s="1" t="s">
         <v>84</v>
       </c>
@@ -9785,7 +10169,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="161" spans="1:15">
+    <row r="161" spans="1:15" ht="15.75">
       <c r="A161" s="1" t="s">
         <v>407</v>
       </c>
@@ -9798,6 +10182,12 @@
       <c r="D161" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E161" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G161" s="1" t="s">
         <v>47</v>
       </c>
@@ -9814,7 +10204,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="162" spans="1:15">
+    <row r="162" spans="1:15" ht="15.75">
       <c r="A162" s="1" t="s">
         <v>409</v>
       </c>
@@ -9826,6 +10216,12 @@
       </c>
       <c r="D162" s="1" t="s">
         <v>18</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>44</v>
@@ -9859,6 +10255,12 @@
       <c r="D163" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E163" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G163" s="1" t="s">
         <v>22</v>
       </c>
@@ -9891,6 +10293,12 @@
       <c r="D164" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E164" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G164" s="1" t="s">
         <v>21</v>
       </c>
@@ -9929,6 +10337,12 @@
       <c r="D165" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E165" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G165" s="1" t="s">
         <v>21</v>
       </c>
@@ -9964,6 +10378,12 @@
       <c r="D166" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E166" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G166" s="1" t="s">
         <v>21</v>
       </c>
@@ -9996,6 +10416,12 @@
       <c r="D167" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E167" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G167" s="1" t="s">
         <v>84</v>
       </c>
@@ -10016,40 +10442,54 @@
       </c>
     </row>
     <row r="168" spans="1:15">
-      <c r="A168" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D168" s="1" t="s">
+      <c r="A168" t="s">
+        <v>917</v>
+      </c>
+      <c r="B168" t="s">
+        <v>918</v>
+      </c>
+      <c r="C168" t="s">
+        <v>80</v>
+      </c>
+      <c r="D168" t="s">
         <v>18</v>
       </c>
-      <c r="G168" s="1" t="s">
+      <c r="E168" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G168" t="s">
+        <v>152</v>
+      </c>
+      <c r="H168" t="s">
         <v>23</v>
       </c>
-      <c r="H168" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I168" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J168" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="I168" t="s">
+        <v>21</v>
+      </c>
+      <c r="J168" t="s">
+        <v>26</v>
+      </c>
+      <c r="K168" t="s">
+        <v>102</v>
+      </c>
+      <c r="L168" t="s">
+        <v>32</v>
+      </c>
+      <c r="M168"/>
+      <c r="N168"/>
       <c r="O168" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="169" spans="1:15">
       <c r="A169" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>17</v>
@@ -10057,6 +10497,12 @@
       <c r="D169" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E169" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G169" s="1" t="s">
         <v>21</v>
       </c>
@@ -10082,12 +10528,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="170" spans="1:15">
+    <row r="170" spans="1:15" ht="15.75">
       <c r="A170" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>80</v>
@@ -10095,6 +10541,12 @@
       <c r="D170" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E170" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G170" s="1" t="s">
         <v>21</v>
       </c>
@@ -10116,10 +10568,10 @@
     </row>
     <row r="171" spans="1:15">
       <c r="A171" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>36</v>
@@ -10127,6 +10579,12 @@
       <c r="D171" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E171" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G171" s="1" t="s">
         <v>72</v>
       </c>
@@ -10151,10 +10609,10 @@
     </row>
     <row r="172" spans="1:15">
       <c r="A172" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>41</v>
@@ -10162,6 +10620,12 @@
       <c r="D172" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E172" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G172" s="1" t="s">
         <v>21</v>
       </c>
@@ -10186,10 +10650,10 @@
     </row>
     <row r="173" spans="1:15">
       <c r="A173" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>17</v>
@@ -10197,6 +10661,12 @@
       <c r="D173" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E173" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G173" s="1" t="s">
         <v>21</v>
       </c>
@@ -10224,10 +10694,10 @@
     </row>
     <row r="174" spans="1:15">
       <c r="A174" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>36</v>
@@ -10235,6 +10705,12 @@
       <c r="D174" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E174" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G174" s="1" t="s">
         <v>23</v>
       </c>
@@ -10259,10 +10735,10 @@
     </row>
     <row r="175" spans="1:15">
       <c r="A175" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>36</v>
@@ -10270,6 +10746,12 @@
       <c r="D175" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E175" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G175" s="1" t="s">
         <v>21</v>
       </c>
@@ -10294,10 +10776,10 @@
     </row>
     <row r="176" spans="1:15">
       <c r="A176" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>17</v>
@@ -10305,6 +10787,12 @@
       <c r="D176" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E176" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G176" s="1" t="s">
         <v>21</v>
       </c>
@@ -10330,12 +10818,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="177" spans="1:15">
+    <row r="177" spans="1:15" ht="15.75">
       <c r="A177" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>80</v>
@@ -10343,6 +10831,12 @@
       <c r="D177" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E177" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G177" s="1" t="s">
         <v>21</v>
       </c>
@@ -10362,12 +10856,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="178" spans="1:15">
+    <row r="178" spans="1:15" ht="15.75">
       <c r="A178" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>36</v>
@@ -10375,6 +10869,12 @@
       <c r="D178" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E178" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G178" s="1" t="s">
         <v>21</v>
       </c>
@@ -10393,10 +10893,10 @@
     </row>
     <row r="179" spans="1:15">
       <c r="A179" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>36</v>
@@ -10404,6 +10904,12 @@
       <c r="D179" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E179" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G179" s="1" t="s">
         <v>21</v>
       </c>
@@ -10425,10 +10931,10 @@
     </row>
     <row r="180" spans="1:15">
       <c r="A180" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>36</v>
@@ -10436,6 +10942,12 @@
       <c r="D180" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E180" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G180" s="1" t="s">
         <v>38</v>
       </c>
@@ -10460,10 +10972,10 @@
     </row>
     <row r="181" spans="1:15">
       <c r="A181" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>36</v>
@@ -10471,6 +10983,12 @@
       <c r="D181" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E181" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G181" s="1" t="s">
         <v>21</v>
       </c>
@@ -10492,10 +11010,10 @@
     </row>
     <row r="182" spans="1:15">
       <c r="A182" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>41</v>
@@ -10503,6 +11021,12 @@
       <c r="D182" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E182" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G182" s="1" t="s">
         <v>223</v>
       </c>
@@ -10513,7 +11037,7 @@
         <v>47</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K182" s="1" t="s">
         <v>68</v>
@@ -10524,10 +11048,10 @@
     </row>
     <row r="183" spans="1:15">
       <c r="A183" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>36</v>
@@ -10535,6 +11059,12 @@
       <c r="D183" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E183" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G183" s="1" t="s">
         <v>21</v>
       </c>
@@ -10551,7 +11081,7 @@
         <v>22</v>
       </c>
       <c r="L183" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="M183" s="1" t="s">
         <v>124</v>
@@ -10560,12 +11090,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="184" spans="1:15">
+    <row r="184" spans="1:15" ht="15.75">
       <c r="A184" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>41</v>
@@ -10573,6 +11103,12 @@
       <c r="D184" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E184" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G184" s="1" t="s">
         <v>60</v>
       </c>
@@ -10591,10 +11127,10 @@
     </row>
     <row r="185" spans="1:15">
       <c r="A185" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>17</v>
@@ -10602,6 +11138,12 @@
       <c r="D185" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E185" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G185" s="1" t="s">
         <v>21</v>
       </c>
@@ -10615,7 +11157,7 @@
         <v>26</v>
       </c>
       <c r="K185" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="O185" s="1" t="s">
         <v>29</v>
@@ -10623,10 +11165,10 @@
     </row>
     <row r="186" spans="1:15">
       <c r="A186" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>41</v>
@@ -10634,6 +11176,12 @@
       <c r="D186" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E186" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G186" s="1" t="s">
         <v>22</v>
       </c>
@@ -10658,10 +11206,10 @@
     </row>
     <row r="187" spans="1:15">
       <c r="A187" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>17</v>
@@ -10669,6 +11217,12 @@
       <c r="D187" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E187" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G187" s="1" t="s">
         <v>21</v>
       </c>
@@ -10688,12 +11242,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="188" spans="1:15">
+    <row r="188" spans="1:15" ht="15.75">
       <c r="A188" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>41</v>
@@ -10701,6 +11255,12 @@
       <c r="D188" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E188" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="F188" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G188" s="1" t="s">
         <v>47</v>
       </c>
@@ -10722,10 +11282,10 @@
     </row>
     <row r="189" spans="1:15">
       <c r="A189" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>17</v>
@@ -10733,6 +11293,12 @@
       <c r="D189" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E189" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G189" s="1" t="s">
         <v>21</v>
       </c>
@@ -10758,12 +11324,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="190" spans="1:15">
+    <row r="190" spans="1:15" ht="15.75">
       <c r="A190" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>80</v>
@@ -10771,6 +11337,12 @@
       <c r="D190" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E190" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F190" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G190" s="1" t="s">
         <v>44</v>
       </c>
@@ -10792,10 +11364,10 @@
     </row>
     <row r="191" spans="1:15">
       <c r="A191" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>17</v>
@@ -10803,6 +11375,12 @@
       <c r="D191" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E191" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G191" s="1" t="s">
         <v>21</v>
       </c>
@@ -10830,10 +11408,10 @@
     </row>
     <row r="192" spans="1:15">
       <c r="A192" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>36</v>
@@ -10841,6 +11419,12 @@
       <c r="D192" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E192" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G192" s="1" t="s">
         <v>21</v>
       </c>
@@ -10862,10 +11446,10 @@
     </row>
     <row r="193" spans="1:15">
       <c r="A193" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>36</v>
@@ -10873,6 +11457,12 @@
       <c r="D193" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E193" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G193" s="1" t="s">
         <v>21</v>
       </c>
@@ -10900,10 +11490,10 @@
     </row>
     <row r="194" spans="1:15">
       <c r="A194" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>17</v>
@@ -10911,6 +11501,12 @@
       <c r="D194" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E194" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G194" s="1" t="s">
         <v>21</v>
       </c>
@@ -10932,10 +11528,10 @@
     </row>
     <row r="195" spans="1:15">
       <c r="A195" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>80</v>
@@ -10943,6 +11539,12 @@
       <c r="D195" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E195" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G195" s="1" t="s">
         <v>21</v>
       </c>
@@ -10961,10 +11563,10 @@
     </row>
     <row r="196" spans="1:15">
       <c r="A196" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>36</v>
@@ -10972,6 +11574,12 @@
       <c r="D196" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E196" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G196" s="1" t="s">
         <v>84</v>
       </c>
@@ -10999,10 +11607,10 @@
     </row>
     <row r="197" spans="1:15">
       <c r="A197" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>80</v>
@@ -11010,6 +11618,12 @@
       <c r="D197" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E197" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G197" s="1" t="s">
         <v>121</v>
       </c>
@@ -11017,7 +11631,7 @@
         <v>63</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J197" s="1" t="s">
         <v>43</v>
@@ -11028,10 +11642,10 @@
     </row>
     <row r="198" spans="1:15">
       <c r="A198" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>36</v>
@@ -11039,6 +11653,12 @@
       <c r="D198" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E198" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G198" s="1" t="s">
         <v>47</v>
       </c>
@@ -11063,10 +11683,10 @@
     </row>
     <row r="199" spans="1:15">
       <c r="A199" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>80</v>
@@ -11074,6 +11694,12 @@
       <c r="D199" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E199" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F199" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G199" s="1" t="s">
         <v>121</v>
       </c>
@@ -11101,10 +11727,10 @@
     </row>
     <row r="200" spans="1:15">
       <c r="A200" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>36</v>
@@ -11112,6 +11738,12 @@
       <c r="D200" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E200" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G200" s="1" t="s">
         <v>21</v>
       </c>
@@ -11139,10 +11771,10 @@
     </row>
     <row r="201" spans="1:15">
       <c r="A201" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>36</v>
@@ -11150,6 +11782,12 @@
       <c r="D201" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E201" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G201" s="1" t="s">
         <v>22</v>
       </c>
@@ -11174,10 +11812,10 @@
     </row>
     <row r="202" spans="1:15">
       <c r="A202" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>36</v>
@@ -11185,6 +11823,12 @@
       <c r="D202" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E202" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F202" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G202" s="1" t="s">
         <v>22</v>
       </c>
@@ -11206,10 +11850,10 @@
     </row>
     <row r="203" spans="1:15">
       <c r="A203" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>41</v>
@@ -11217,6 +11861,12 @@
       <c r="D203" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E203" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F203" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="G203" s="1" t="s">
         <v>223</v>
       </c>
@@ -11235,10 +11885,10 @@
     </row>
     <row r="204" spans="1:15">
       <c r="A204" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>41</v>
@@ -11246,6 +11896,12 @@
       <c r="D204" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E204" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F204" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G204" s="1" t="s">
         <v>21</v>
       </c>
@@ -11270,10 +11926,10 @@
     </row>
     <row r="205" spans="1:15">
       <c r="A205" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>17</v>
@@ -11281,6 +11937,12 @@
       <c r="D205" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E205" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F205" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G205" s="1" t="s">
         <v>21</v>
       </c>
@@ -11302,10 +11964,10 @@
     </row>
     <row r="206" spans="1:15">
       <c r="A206" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>41</v>
@@ -11313,6 +11975,12 @@
       <c r="D206" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E206" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F206" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G206" s="1" t="s">
         <v>54</v>
       </c>
@@ -11320,7 +11988,7 @@
         <v>28</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="J206" s="1" t="s">
         <v>38</v>
@@ -11334,10 +12002,10 @@
     </row>
     <row r="207" spans="1:15">
       <c r="A207" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>36</v>
@@ -11345,6 +12013,12 @@
       <c r="D207" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E207" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F207" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G207" s="1" t="s">
         <v>44</v>
       </c>
@@ -11363,10 +12037,10 @@
     </row>
     <row r="208" spans="1:15">
       <c r="A208" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>17</v>
@@ -11374,6 +12048,12 @@
       <c r="D208" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E208" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F208" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G208" s="1" t="s">
         <v>44</v>
       </c>
@@ -11392,10 +12072,10 @@
     </row>
     <row r="209" spans="1:15">
       <c r="A209" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>36</v>
@@ -11403,6 +12083,12 @@
       <c r="D209" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E209" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F209" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G209" s="1" t="s">
         <v>21</v>
       </c>
@@ -11424,10 +12110,10 @@
     </row>
     <row r="210" spans="1:15">
       <c r="A210" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>80</v>
@@ -11435,6 +12121,12 @@
       <c r="D210" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E210" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F210" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G210" s="1" t="s">
         <v>21</v>
       </c>
@@ -11459,10 +12151,10 @@
     </row>
     <row r="211" spans="1:15">
       <c r="A211" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>17</v>
@@ -11470,6 +12162,12 @@
       <c r="D211" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E211" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F211" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G211" s="1" t="s">
         <v>21</v>
       </c>
@@ -11494,10 +12192,10 @@
     </row>
     <row r="212" spans="1:15">
       <c r="A212" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>36</v>
@@ -11505,6 +12203,12 @@
       <c r="D212" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E212" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F212" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G212" s="1" t="s">
         <v>21</v>
       </c>
@@ -11515,7 +12219,7 @@
         <v>23</v>
       </c>
       <c r="J212" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K212" s="1" t="s">
         <v>26</v>
@@ -11529,10 +12233,10 @@
     </row>
     <row r="213" spans="1:15">
       <c r="A213" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>80</v>
@@ -11540,6 +12244,12 @@
       <c r="D213" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E213" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F213" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="G213" s="1" t="s">
         <v>21</v>
       </c>
@@ -11570,10 +12280,10 @@
     </row>
     <row r="214" spans="1:15">
       <c r="A214" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>36</v>
@@ -11581,6 +12291,12 @@
       <c r="D214" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E214" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F214" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G214" s="1" t="s">
         <v>21</v>
       </c>
@@ -11594,7 +12310,7 @@
         <v>26</v>
       </c>
       <c r="K214" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="O214" s="1" t="s">
         <v>29</v>
@@ -11602,10 +12318,10 @@
     </row>
     <row r="215" spans="1:15">
       <c r="A215" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>36</v>
@@ -11613,6 +12329,12 @@
       <c r="D215" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E215" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F215" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G215" s="1" t="s">
         <v>21</v>
       </c>
@@ -11637,10 +12359,10 @@
     </row>
     <row r="216" spans="1:15">
       <c r="A216" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>41</v>
@@ -11648,6 +12370,12 @@
       <c r="D216" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E216" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F216" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G216" s="1" t="s">
         <v>23</v>
       </c>
@@ -11667,7 +12395,7 @@
         <v>28</v>
       </c>
       <c r="M216" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="N216" s="1" t="s">
         <v>68</v>
@@ -11678,10 +12406,10 @@
     </row>
     <row r="217" spans="1:15">
       <c r="A217" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>17</v>
@@ -11689,6 +12417,12 @@
       <c r="D217" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E217" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F217" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G217" s="1" t="s">
         <v>21</v>
       </c>
@@ -11713,10 +12447,10 @@
     </row>
     <row r="218" spans="1:15">
       <c r="A218" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>36</v>
@@ -11724,6 +12458,12 @@
       <c r="D218" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E218" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F218" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G218" s="1" t="s">
         <v>23</v>
       </c>
@@ -11751,10 +12491,10 @@
     </row>
     <row r="219" spans="1:15">
       <c r="A219" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>80</v>
@@ -11762,6 +12502,12 @@
       <c r="D219" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E219" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F219" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G219" s="1" t="s">
         <v>21</v>
       </c>
@@ -11789,10 +12535,10 @@
     </row>
     <row r="220" spans="1:15">
       <c r="A220" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>41</v>
@@ -11800,6 +12546,12 @@
       <c r="D220" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E220" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F220" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="G220" s="1" t="s">
         <v>21</v>
       </c>
@@ -11818,10 +12570,10 @@
     </row>
     <row r="221" spans="1:15">
       <c r="A221" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>36</v>
@@ -11829,6 +12581,12 @@
       <c r="D221" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E221" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F221" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G221" s="1" t="s">
         <v>44</v>
       </c>
@@ -11850,10 +12608,10 @@
     </row>
     <row r="222" spans="1:15">
       <c r="A222" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>41</v>
@@ -11861,6 +12619,12 @@
       <c r="D222" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E222" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F222" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G222" s="1" t="s">
         <v>22</v>
       </c>
@@ -11885,10 +12649,10 @@
     </row>
     <row r="223" spans="1:15">
       <c r="A223" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>41</v>
@@ -11896,6 +12660,12 @@
       <c r="D223" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E223" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F223" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="G223" s="1" t="s">
         <v>53</v>
       </c>
@@ -11926,10 +12696,10 @@
     </row>
     <row r="224" spans="1:15">
       <c r="A224" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>80</v>
@@ -11937,6 +12707,12 @@
       <c r="D224" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E224" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F224" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="G224" s="1" t="s">
         <v>21</v>
       </c>
@@ -11947,7 +12723,7 @@
         <v>124</v>
       </c>
       <c r="J224" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="O224" s="1" t="s">
         <v>29</v>
@@ -11955,10 +12731,10 @@
     </row>
     <row r="225" spans="1:15">
       <c r="A225" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>17</v>
@@ -11966,6 +12742,12 @@
       <c r="D225" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E225" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F225" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G225" s="1" t="s">
         <v>21</v>
       </c>
@@ -11990,10 +12772,10 @@
     </row>
     <row r="226" spans="1:15">
       <c r="A226" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>36</v>
@@ -12001,6 +12783,12 @@
       <c r="D226" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E226" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F226" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G226" s="1" t="s">
         <v>21</v>
       </c>
@@ -12008,10 +12796,10 @@
         <v>47</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="K226" s="1" t="s">
         <v>25</v>
@@ -12025,10 +12813,10 @@
     </row>
     <row r="227" spans="1:15">
       <c r="A227" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>36</v>
@@ -12036,6 +12824,12 @@
       <c r="D227" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E227" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F227" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G227" s="1" t="s">
         <v>84</v>
       </c>
@@ -12057,10 +12851,10 @@
     </row>
     <row r="228" spans="1:15">
       <c r="A228" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>36</v>
@@ -12068,6 +12862,12 @@
       <c r="D228" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E228" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F228" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G228" s="1" t="s">
         <v>21</v>
       </c>
@@ -12086,10 +12886,10 @@
     </row>
     <row r="229" spans="1:15">
       <c r="A229" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>17</v>
@@ -12097,6 +12897,12 @@
       <c r="D229" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E229" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F229" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G229" s="1" t="s">
         <v>21</v>
       </c>
@@ -12127,10 +12933,10 @@
     </row>
     <row r="230" spans="1:15">
       <c r="A230" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>17</v>
@@ -12138,6 +12944,12 @@
       <c r="D230" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E230" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F230" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G230" s="1" t="s">
         <v>21</v>
       </c>
@@ -12145,10 +12957,10 @@
         <v>47</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="K230" s="1" t="s">
         <v>26</v>
@@ -12162,10 +12974,10 @@
     </row>
     <row r="231" spans="1:15">
       <c r="A231" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>41</v>
@@ -12173,6 +12985,12 @@
       <c r="D231" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E231" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F231" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G231" s="1" t="s">
         <v>21</v>
       </c>
@@ -12197,10 +13015,10 @@
     </row>
     <row r="232" spans="1:15">
       <c r="A232" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>36</v>
@@ -12208,6 +13026,12 @@
       <c r="D232" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E232" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F232" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G232" s="1" t="s">
         <v>21</v>
       </c>
@@ -12229,10 +13053,10 @@
     </row>
     <row r="233" spans="1:15">
       <c r="A233" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>36</v>
@@ -12240,6 +13064,12 @@
       <c r="D233" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E233" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F233" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G233" s="1" t="s">
         <v>21</v>
       </c>
@@ -12258,10 +13088,10 @@
     </row>
     <row r="234" spans="1:15">
       <c r="A234" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>36</v>
@@ -12269,6 +13099,12 @@
       <c r="D234" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E234" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F234" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G234" s="1" t="s">
         <v>21</v>
       </c>
@@ -12290,10 +13126,10 @@
     </row>
     <row r="235" spans="1:15">
       <c r="A235" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>36</v>
@@ -12301,6 +13137,12 @@
       <c r="D235" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E235" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F235" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G235" s="1" t="s">
         <v>24</v>
       </c>
@@ -12322,10 +13164,10 @@
     </row>
     <row r="236" spans="1:15">
       <c r="A236" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>41</v>
@@ -12333,6 +13175,12 @@
       <c r="D236" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E236" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F236" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G236" s="1" t="s">
         <v>43</v>
       </c>
@@ -12360,10 +13208,10 @@
     </row>
     <row r="237" spans="1:15">
       <c r="A237" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>17</v>
@@ -12371,6 +13219,12 @@
       <c r="D237" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E237" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F237" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G237" s="1" t="s">
         <v>21</v>
       </c>
@@ -12398,10 +13252,10 @@
     </row>
     <row r="238" spans="1:15">
       <c r="A238" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>80</v>
@@ -12409,6 +13263,12 @@
       <c r="D238" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E238" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F238" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G238" s="1" t="s">
         <v>23</v>
       </c>
@@ -12430,10 +13290,10 @@
     </row>
     <row r="239" spans="1:15">
       <c r="A239" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>17</v>
@@ -12441,6 +13301,12 @@
       <c r="D239" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E239" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F239" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G239" s="1" t="s">
         <v>44</v>
       </c>
@@ -12462,10 +13328,10 @@
     </row>
     <row r="240" spans="1:15">
       <c r="A240" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>41</v>
@@ -12473,6 +13339,12 @@
       <c r="D240" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E240" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F240" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G240" s="1" t="s">
         <v>47</v>
       </c>
@@ -12494,10 +13366,10 @@
     </row>
     <row r="241" spans="1:15">
       <c r="A241" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>17</v>
@@ -12505,6 +13377,12 @@
       <c r="D241" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E241" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F241" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G241" s="1" t="s">
         <v>21</v>
       </c>
@@ -12532,10 +13410,10 @@
     </row>
     <row r="242" spans="1:15">
       <c r="A242" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>36</v>
@@ -12543,6 +13421,12 @@
       <c r="D242" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E242" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F242" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G242" s="1" t="s">
         <v>21</v>
       </c>
@@ -12570,10 +13454,10 @@
     </row>
     <row r="243" spans="1:15">
       <c r="A243" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>36</v>
@@ -12581,6 +13465,12 @@
       <c r="D243" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E243" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F243" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G243" s="1" t="s">
         <v>21</v>
       </c>
@@ -12599,10 +13489,10 @@
     </row>
     <row r="244" spans="1:15">
       <c r="A244" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>17</v>
@@ -12610,6 +13500,12 @@
       <c r="D244" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E244" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F244" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G244" s="1" t="s">
         <v>21</v>
       </c>
@@ -12634,10 +13530,10 @@
     </row>
     <row r="245" spans="1:15">
       <c r="A245" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>41</v>
@@ -12645,6 +13541,12 @@
       <c r="D245" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E245" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F245" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G245" s="1" t="s">
         <v>21</v>
       </c>
@@ -12661,7 +13563,7 @@
         <v>43</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="O245" s="1" t="s">
         <v>29</v>
@@ -12669,10 +13571,10 @@
     </row>
     <row r="246" spans="1:15">
       <c r="A246" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>80</v>
@@ -12680,6 +13582,12 @@
       <c r="D246" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E246" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F246" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G246" s="1" t="s">
         <v>22</v>
       </c>
@@ -12710,10 +13618,10 @@
     </row>
     <row r="247" spans="1:15">
       <c r="A247" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>36</v>
@@ -12721,6 +13629,12 @@
       <c r="D247" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E247" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F247" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G247" s="1" t="s">
         <v>21</v>
       </c>
@@ -12748,10 +13662,10 @@
     </row>
     <row r="248" spans="1:15">
       <c r="A248" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>41</v>
@@ -12759,6 +13673,12 @@
       <c r="D248" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E248" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F248" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G248" s="1" t="s">
         <v>44</v>
       </c>
@@ -12786,10 +13706,10 @@
     </row>
     <row r="249" spans="1:15">
       <c r="A249" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>17</v>
@@ -12797,6 +13717,12 @@
       <c r="D249" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E249" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F249" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G249" s="1" t="s">
         <v>21</v>
       </c>
@@ -12816,10 +13742,10 @@
         <v>121</v>
       </c>
       <c r="M249" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="N249" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="O249" s="1" t="s">
         <v>29</v>
@@ -12827,10 +13753,10 @@
     </row>
     <row r="250" spans="1:15">
       <c r="A250" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>41</v>
@@ -12838,6 +13764,12 @@
       <c r="D250" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E250" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F250" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G250" s="1" t="s">
         <v>72</v>
       </c>
@@ -12862,10 +13794,10 @@
     </row>
     <row r="251" spans="1:15">
       <c r="A251" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>41</v>
@@ -12873,6 +13805,12 @@
       <c r="D251" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E251" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F251" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G251" s="1" t="s">
         <v>21</v>
       </c>
@@ -12897,10 +13835,10 @@
     </row>
     <row r="252" spans="1:15">
       <c r="A252" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>36</v>
@@ -12908,6 +13846,12 @@
       <c r="D252" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E252" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F252" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G252" s="1" t="s">
         <v>152</v>
       </c>
@@ -12929,10 +13873,10 @@
     </row>
     <row r="253" spans="1:15">
       <c r="A253" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>41</v>
@@ -12940,6 +13884,12 @@
       <c r="D253" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E253" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F253" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G253" s="1" t="s">
         <v>21</v>
       </c>
@@ -12961,10 +13911,10 @@
     </row>
     <row r="254" spans="1:15">
       <c r="A254" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>41</v>
@@ -12972,6 +13922,12 @@
       <c r="D254" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E254" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F254" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="G254" s="1" t="s">
         <v>60</v>
       </c>
@@ -12996,10 +13952,10 @@
     </row>
     <row r="255" spans="1:15">
       <c r="A255" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>36</v>
@@ -13007,6 +13963,12 @@
       <c r="D255" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E255" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F255" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G255" s="1" t="s">
         <v>21</v>
       </c>
@@ -13031,10 +13993,10 @@
     </row>
     <row r="256" spans="1:15">
       <c r="A256" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>41</v>
@@ -13042,6 +14004,12 @@
       <c r="D256" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E256" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F256" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G256" s="1" t="s">
         <v>21</v>
       </c>
@@ -13063,10 +14031,10 @@
     </row>
     <row r="257" spans="1:15">
       <c r="A257" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>36</v>
@@ -13074,6 +14042,12 @@
       <c r="D257" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E257" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F257" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G257" s="1" t="s">
         <v>21</v>
       </c>
@@ -13095,10 +14069,10 @@
     </row>
     <row r="258" spans="1:15">
       <c r="A258" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>36</v>
@@ -13106,6 +14080,12 @@
       <c r="D258" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E258" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F258" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G258" s="1" t="s">
         <v>21</v>
       </c>
@@ -13127,10 +14107,10 @@
     </row>
     <row r="259" spans="1:15">
       <c r="A259" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>36</v>
@@ -13138,6 +14118,12 @@
       <c r="D259" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E259" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F259" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G259" s="1" t="s">
         <v>23</v>
       </c>
@@ -13162,10 +14148,10 @@
     </row>
     <row r="260" spans="1:15">
       <c r="A260" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>36</v>
@@ -13173,6 +14159,12 @@
       <c r="D260" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E260" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F260" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G260" s="1" t="s">
         <v>21</v>
       </c>
@@ -13197,10 +14189,10 @@
     </row>
     <row r="261" spans="1:15">
       <c r="A261" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>80</v>
@@ -13208,6 +14200,12 @@
       <c r="D261" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E261" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F261" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G261" s="1" t="s">
         <v>21</v>
       </c>
@@ -13226,10 +14224,10 @@
     </row>
     <row r="262" spans="1:15">
       <c r="A262" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>80</v>
@@ -13237,6 +14235,12 @@
       <c r="D262" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E262" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F262" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="G262" s="1" t="s">
         <v>21</v>
       </c>
@@ -13247,13 +14251,13 @@
         <v>28</v>
       </c>
       <c r="J262" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="K262" s="1" t="s">
         <v>55</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="O262" s="1" t="s">
         <v>29</v>
@@ -13261,10 +14265,10 @@
     </row>
     <row r="263" spans="1:15">
       <c r="A263" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>41</v>
@@ -13272,6 +14276,12 @@
       <c r="D263" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E263" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F263" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G263" s="1" t="s">
         <v>121</v>
       </c>
@@ -13293,10 +14303,10 @@
     </row>
     <row r="264" spans="1:15">
       <c r="A264" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>41</v>
@@ -13304,6 +14314,12 @@
       <c r="D264" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E264" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F264" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G264" s="1" t="s">
         <v>21</v>
       </c>
@@ -13325,10 +14341,10 @@
     </row>
     <row r="265" spans="1:15">
       <c r="A265" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>36</v>
@@ -13336,6 +14352,12 @@
       <c r="D265" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E265" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F265" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G265" s="1" t="s">
         <v>21</v>
       </c>
@@ -13354,10 +14376,10 @@
     </row>
     <row r="266" spans="1:15">
       <c r="A266" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>41</v>
@@ -13365,6 +14387,12 @@
       <c r="D266" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E266" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F266" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G266" s="1" t="s">
         <v>21</v>
       </c>
@@ -13386,10 +14414,10 @@
     </row>
     <row r="267" spans="1:15">
       <c r="A267" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>36</v>
@@ -13397,6 +14425,12 @@
       <c r="D267" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E267" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F267" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G267" s="1" t="s">
         <v>21</v>
       </c>
@@ -13427,10 +14461,10 @@
     </row>
     <row r="268" spans="1:15">
       <c r="A268" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>36</v>
@@ -13438,6 +14472,12 @@
       <c r="D268" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E268" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F268" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G268" s="1" t="s">
         <v>21</v>
       </c>
@@ -13451,7 +14491,7 @@
         <v>32</v>
       </c>
       <c r="K268" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="L268" s="1" t="s">
         <v>26</v>
@@ -13462,10 +14502,10 @@
     </row>
     <row r="269" spans="1:15">
       <c r="A269" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>41</v>
@@ -13473,6 +14513,12 @@
       <c r="D269" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E269" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F269" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="G269" s="1" t="s">
         <v>21</v>
       </c>
@@ -13503,10 +14549,10 @@
     </row>
     <row r="270" spans="1:15">
       <c r="A270" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>80</v>
@@ -13514,6 +14560,12 @@
       <c r="D270" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E270" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F270" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G270" s="1" t="s">
         <v>44</v>
       </c>
@@ -13535,10 +14587,10 @@
     </row>
     <row r="271" spans="1:15">
       <c r="A271" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>36</v>
@@ -13546,6 +14598,12 @@
       <c r="D271" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E271" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F271" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G271" s="1" t="s">
         <v>23</v>
       </c>
@@ -13573,10 +14631,10 @@
     </row>
     <row r="272" spans="1:15">
       <c r="A272" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>41</v>
@@ -13584,6 +14642,12 @@
       <c r="D272" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E272" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F272" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G272" s="1" t="s">
         <v>21</v>
       </c>
@@ -13614,10 +14678,10 @@
     </row>
     <row r="273" spans="1:15">
       <c r="A273" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>41</v>
@@ -13625,6 +14689,12 @@
       <c r="D273" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E273" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F273" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G273" s="1" t="s">
         <v>21</v>
       </c>
@@ -13649,10 +14719,10 @@
     </row>
     <row r="274" spans="1:15">
       <c r="A274" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>17</v>
@@ -13660,6 +14730,12 @@
       <c r="D274" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E274" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F274" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G274" s="1" t="s">
         <v>47</v>
       </c>
@@ -13678,10 +14754,10 @@
     </row>
     <row r="275" spans="1:15">
       <c r="A275" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>41</v>
@@ -13689,6 +14765,12 @@
       <c r="D275" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E275" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F275" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="G275" s="1" t="s">
         <v>43</v>
       </c>
@@ -13716,10 +14798,10 @@
     </row>
     <row r="276" spans="1:15">
       <c r="A276" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>36</v>
@@ -13727,6 +14809,12 @@
       <c r="D276" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E276" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F276" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G276" s="1" t="s">
         <v>105</v>
       </c>
@@ -13748,10 +14836,10 @@
     </row>
     <row r="277" spans="1:15">
       <c r="A277" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>36</v>
@@ -13759,6 +14847,12 @@
       <c r="D277" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E277" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F277" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G277" s="1" t="s">
         <v>84</v>
       </c>
@@ -13789,10 +14883,10 @@
     </row>
     <row r="278" spans="1:15">
       <c r="A278" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>36</v>
@@ -13800,6 +14894,12 @@
       <c r="D278" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E278" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F278" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G278" s="1" t="s">
         <v>84</v>
       </c>
@@ -13821,10 +14921,10 @@
     </row>
     <row r="279" spans="1:15">
       <c r="A279" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>80</v>
@@ -13832,6 +14932,12 @@
       <c r="D279" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E279" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F279" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G279" s="1" t="s">
         <v>21</v>
       </c>
@@ -13853,10 +14959,10 @@
     </row>
     <row r="280" spans="1:15">
       <c r="A280" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>36</v>
@@ -13864,6 +14970,12 @@
       <c r="D280" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E280" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F280" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G280" s="1" t="s">
         <v>121</v>
       </c>
@@ -13885,10 +14997,10 @@
     </row>
     <row r="281" spans="1:15">
       <c r="A281" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>41</v>
@@ -13896,6 +15008,12 @@
       <c r="D281" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E281" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F281" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G281" s="1" t="s">
         <v>121</v>
       </c>
@@ -13920,10 +15038,10 @@
     </row>
     <row r="282" spans="1:15">
       <c r="A282" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>17</v>
@@ -13931,6 +15049,12 @@
       <c r="D282" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E282" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F282" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G282" s="1" t="s">
         <v>21</v>
       </c>
@@ -13952,10 +15076,10 @@
     </row>
     <row r="283" spans="1:15">
       <c r="A283" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>41</v>
@@ -13963,6 +15087,12 @@
       <c r="D283" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E283" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F283" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G283" s="1" t="s">
         <v>22</v>
       </c>
@@ -13984,10 +15114,10 @@
     </row>
     <row r="284" spans="1:15">
       <c r="A284" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>17</v>
@@ -13995,6 +15125,12 @@
       <c r="D284" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E284" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F284" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G284" s="1" t="s">
         <v>23</v>
       </c>
@@ -14005,7 +15141,7 @@
         <v>24</v>
       </c>
       <c r="J284" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="K284" s="1" t="s">
         <v>169</v>
@@ -14022,10 +15158,10 @@
     </row>
     <row r="285" spans="1:15">
       <c r="A285" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>41</v>
@@ -14033,6 +15169,12 @@
       <c r="D285" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E285" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F285" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G285" s="1" t="s">
         <v>21</v>
       </c>
@@ -14060,10 +15202,10 @@
     </row>
     <row r="286" spans="1:15">
       <c r="A286" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>36</v>
@@ -14071,6 +15213,12 @@
       <c r="D286" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E286" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F286" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G286" s="1" t="s">
         <v>21</v>
       </c>
@@ -14095,10 +15243,10 @@
     </row>
     <row r="287" spans="1:15">
       <c r="A287" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>17</v>
@@ -14106,6 +15254,12 @@
       <c r="D287" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E287" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F287" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G287" s="1" t="s">
         <v>21</v>
       </c>
@@ -14133,10 +15287,10 @@
     </row>
     <row r="288" spans="1:15">
       <c r="A288" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>36</v>
@@ -14144,6 +15298,12 @@
       <c r="D288" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E288" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F288" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G288" s="1" t="s">
         <v>21</v>
       </c>
@@ -14165,10 +15325,10 @@
     </row>
     <row r="289" spans="1:15">
       <c r="A289" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>80</v>
@@ -14176,6 +15336,12 @@
       <c r="D289" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E289" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F289" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G289" s="1" t="s">
         <v>21</v>
       </c>
@@ -14200,10 +15366,10 @@
     </row>
     <row r="290" spans="1:15">
       <c r="A290" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>80</v>
@@ -14211,6 +15377,12 @@
       <c r="D290" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E290" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F290" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G290" s="1" t="s">
         <v>44</v>
       </c>
@@ -14235,10 +15407,10 @@
     </row>
     <row r="291" spans="1:15">
       <c r="A291" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>80</v>
@@ -14246,6 +15418,12 @@
       <c r="D291" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E291" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F291" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="G291" s="1" t="s">
         <v>22</v>
       </c>
@@ -14253,7 +15431,7 @@
         <v>54</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="J291" s="1" t="s">
         <v>47</v>
@@ -14262,7 +15440,7 @@
         <v>102</v>
       </c>
       <c r="L291" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="O291" s="1" t="s">
         <v>29</v>
@@ -14270,10 +15448,10 @@
     </row>
     <row r="292" spans="1:15">
       <c r="A292" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>17</v>
@@ -14281,6 +15459,12 @@
       <c r="D292" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E292" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F292" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G292" s="1" t="s">
         <v>24</v>
       </c>
@@ -14305,10 +15489,10 @@
     </row>
     <row r="293" spans="1:15">
       <c r="A293" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>17</v>
@@ -14316,6 +15500,12 @@
       <c r="D293" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E293" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F293" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G293" s="1" t="s">
         <v>38</v>
       </c>
@@ -14337,10 +15527,10 @@
     </row>
     <row r="294" spans="1:15">
       <c r="A294" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>41</v>
@@ -14348,6 +15538,12 @@
       <c r="D294" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E294" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F294" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="G294" s="1" t="s">
         <v>47</v>
       </c>
@@ -14366,10 +15562,10 @@
     </row>
     <row r="295" spans="1:15">
       <c r="A295" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>80</v>
@@ -14377,6 +15573,12 @@
       <c r="D295" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E295" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F295" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G295" s="1" t="s">
         <v>152</v>
       </c>
@@ -14407,10 +15609,10 @@
     </row>
     <row r="296" spans="1:15">
       <c r="A296" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>36</v>
@@ -14418,6 +15620,12 @@
       <c r="D296" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E296" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F296" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G296" s="1" t="s">
         <v>23</v>
       </c>
@@ -14439,10 +15647,10 @@
     </row>
     <row r="297" spans="1:15">
       <c r="A297" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>80</v>
@@ -14450,6 +15658,12 @@
       <c r="D297" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E297" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F297" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G297" s="1" t="s">
         <v>21</v>
       </c>
@@ -14471,10 +15685,10 @@
     </row>
     <row r="298" spans="1:15">
       <c r="A298" s="1" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>36</v>
@@ -14482,6 +15696,12 @@
       <c r="D298" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E298" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F298" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G298" s="1" t="s">
         <v>32</v>
       </c>
@@ -14512,10 +15732,10 @@
     </row>
     <row r="299" spans="1:15">
       <c r="A299" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>80</v>
@@ -14523,6 +15743,12 @@
       <c r="D299" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="E299" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F299" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="G299" s="1" t="s">
         <v>68</v>
       </c>
@@ -14544,10 +15770,10 @@
     </row>
     <row r="300" spans="1:15">
       <c r="A300" s="1" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>41</v>
@@ -14555,6 +15781,12 @@
       <c r="D300" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E300" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F300" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G300" s="1" t="s">
         <v>23</v>
       </c>
@@ -14579,10 +15811,10 @@
     </row>
     <row r="301" spans="1:15">
       <c r="A301" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>17</v>
@@ -14590,6 +15822,12 @@
       <c r="D301" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="E301" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F301" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G301" s="1" t="s">
         <v>21</v>
       </c>
@@ -14611,10 +15849,10 @@
     </row>
     <row r="302" spans="1:15">
       <c r="A302" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>36</v>
@@ -14643,10 +15881,10 @@
     </row>
     <row r="303" spans="1:15">
       <c r="A303" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>41</v>
@@ -14658,7 +15896,7 @@
         <v>92</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G303" s="1" t="s">
         <v>21</v>
@@ -14678,10 +15916,10 @@
     </row>
     <row r="304" spans="1:15">
       <c r="A304" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>36</v>
@@ -14693,7 +15931,7 @@
         <v>92</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G304" s="1" t="s">
         <v>22</v>
@@ -14705,10 +15943,10 @@
         <v>55</v>
       </c>
       <c r="J304" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="K304" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="L304" s="1" t="s">
         <v>43</v>
@@ -14725,10 +15963,10 @@
     </row>
     <row r="305" spans="1:15">
       <c r="A305" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>17</v>
@@ -14740,7 +15978,7 @@
         <v>42</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G305" s="1" t="s">
         <v>44</v>
@@ -14763,10 +16001,10 @@
     </row>
     <row r="306" spans="1:15">
       <c r="A306" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>36</v>
@@ -14775,10 +16013,10 @@
         <v>18</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G306" s="1" t="s">
         <v>22</v>
@@ -14804,10 +16042,10 @@
     </row>
     <row r="307" spans="1:15">
       <c r="A307" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>36</v>
@@ -14819,7 +16057,7 @@
         <v>37</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G307" s="1" t="s">
         <v>21</v>
@@ -14848,10 +16086,10 @@
     </row>
     <row r="308" spans="1:15">
       <c r="A308" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>41</v>
@@ -14860,10 +16098,10 @@
         <v>18</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>22</v>
@@ -14892,10 +16130,10 @@
     </row>
     <row r="309" spans="1:15">
       <c r="A309" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>41</v>
@@ -14907,7 +16145,7 @@
         <v>37</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G309" s="1" t="s">
         <v>21</v>
@@ -14930,10 +16168,10 @@
     </row>
     <row r="310" spans="1:15">
       <c r="A310" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>41</v>
@@ -14945,7 +16183,7 @@
         <v>37</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G310" s="1" t="s">
         <v>21</v>
@@ -14968,10 +16206,10 @@
     </row>
     <row r="311" spans="1:15">
       <c r="A311" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>80</v>
@@ -14980,10 +16218,10 @@
         <v>18</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>21</v>
@@ -15012,10 +16250,10 @@
     </row>
     <row r="312" spans="1:15">
       <c r="A312" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>41</v>
@@ -15027,7 +16265,7 @@
         <v>42</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G312" s="1" t="s">
         <v>44</v>
@@ -15047,10 +16285,10 @@
     </row>
     <row r="313" spans="1:15">
       <c r="A313" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>17</v>
@@ -15062,7 +16300,7 @@
         <v>59</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G313" s="1" t="s">
         <v>47</v>
@@ -15082,10 +16320,10 @@
     </row>
     <row r="314" spans="1:15">
       <c r="A314" s="1" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>36</v>
@@ -15097,7 +16335,7 @@
         <v>59</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G314" s="1" t="s">
         <v>47</v>
@@ -15117,10 +16355,10 @@
     </row>
     <row r="315" spans="1:15">
       <c r="A315" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>80</v>
@@ -15132,7 +16370,7 @@
         <v>92</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>21</v>
@@ -15155,10 +16393,10 @@
     </row>
     <row r="316" spans="1:15">
       <c r="A316" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>80</v>
@@ -15170,7 +16408,7 @@
         <v>92</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G316" s="1" t="s">
         <v>22</v>
@@ -15193,10 +16431,10 @@
     </row>
     <row r="317" spans="1:15">
       <c r="A317" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>36</v>
@@ -15205,10 +16443,10 @@
         <v>18</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G317" s="1" t="s">
         <v>21</v>
@@ -15234,10 +16472,10 @@
     </row>
     <row r="318" spans="1:15">
       <c r="A318" s="1" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>41</v>
@@ -15249,7 +16487,7 @@
         <v>37</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G318" s="1" t="s">
         <v>21</v>
@@ -15269,10 +16507,10 @@
     </row>
     <row r="319" spans="1:15">
       <c r="A319" s="1" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>17</v>
@@ -15281,10 +16519,10 @@
         <v>58</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G319" s="1" t="s">
         <v>55</v>
@@ -15304,10 +16542,10 @@
     </row>
     <row r="320" spans="1:15">
       <c r="A320" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>36</v>
@@ -15316,10 +16554,10 @@
         <v>18</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G320" s="1" t="s">
         <v>21</v>
@@ -15342,10 +16580,10 @@
     </row>
     <row r="321" spans="1:15">
       <c r="A321" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>41</v>
@@ -15357,7 +16595,7 @@
         <v>92</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G321" s="1" t="s">
         <v>21</v>
@@ -15386,10 +16624,10 @@
     </row>
     <row r="322" spans="1:15">
       <c r="A322" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>36</v>
@@ -15398,10 +16636,10 @@
         <v>50</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G322" s="1" t="s">
         <v>21</v>
@@ -15427,10 +16665,10 @@
     </row>
     <row r="323" spans="1:15">
       <c r="A323" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>36</v>
@@ -15442,7 +16680,7 @@
         <v>92</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G323" s="1" t="s">
         <v>21</v>
@@ -15465,10 +16703,10 @@
     </row>
     <row r="324" spans="1:15">
       <c r="A324" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>41</v>
@@ -15477,10 +16715,10 @@
         <v>50</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>22</v>
@@ -15506,10 +16744,10 @@
     </row>
     <row r="325" spans="1:15">
       <c r="A325" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>17</v>
@@ -15521,7 +16759,7 @@
         <v>59</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G325" s="1" t="s">
         <v>21</v>
@@ -15547,10 +16785,10 @@
     </row>
     <row r="326" spans="1:15">
       <c r="A326" s="1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>36</v>
@@ -15562,7 +16800,7 @@
         <v>37</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G326" s="1" t="s">
         <v>21</v>
@@ -15588,10 +16826,10 @@
     </row>
     <row r="327" spans="1:15">
       <c r="A327" s="1" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>80</v>
@@ -15603,7 +16841,7 @@
         <v>37</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>47</v>
@@ -15626,10 +16864,10 @@
     </row>
     <row r="328" spans="1:15">
       <c r="A328" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>17</v>
@@ -15641,7 +16879,7 @@
         <v>37</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>21</v>
@@ -15667,10 +16905,10 @@
     </row>
     <row r="329" spans="1:15">
       <c r="A329" s="1" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>41</v>
@@ -15682,7 +16920,7 @@
         <v>42</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>44</v>
@@ -15702,10 +16940,10 @@
     </row>
     <row r="330" spans="1:15">
       <c r="A330" s="1" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>17</v>
@@ -15717,7 +16955,7 @@
         <v>37</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>21</v>
@@ -15743,10 +16981,10 @@
     </row>
     <row r="331" spans="1:15">
       <c r="A331" s="1" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>41</v>
@@ -15758,7 +16996,7 @@
         <v>37</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>21</v>
@@ -15767,7 +17005,7 @@
         <v>47</v>
       </c>
       <c r="I331" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="J331" s="1" t="s">
         <v>22</v>
@@ -15779,7 +17017,7 @@
         <v>26</v>
       </c>
       <c r="M331" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="O331" s="1" t="s">
         <v>29</v>
@@ -15787,10 +17025,10 @@
     </row>
     <row r="332" spans="1:15">
       <c r="A332" s="1" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>41</v>
@@ -15799,10 +17037,10 @@
         <v>58</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>22</v>
@@ -15825,10 +17063,10 @@
     </row>
     <row r="333" spans="1:15">
       <c r="A333" s="1" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>36</v>
@@ -15837,10 +17075,10 @@
         <v>50</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>23</v>
@@ -15866,10 +17104,10 @@
     </row>
     <row r="334" spans="1:15">
       <c r="A334" s="1" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>41</v>
@@ -15881,7 +17119,7 @@
         <v>37</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>21</v>
@@ -15896,7 +17134,7 @@
         <v>33</v>
       </c>
       <c r="K334" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="O334" s="1" t="s">
         <v>29</v>
@@ -15904,10 +17142,10 @@
     </row>
     <row r="335" spans="1:15">
       <c r="A335" s="1" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>36</v>
@@ -15916,10 +17154,10 @@
         <v>18</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>21</v>
@@ -15942,10 +17180,10 @@
     </row>
     <row r="336" spans="1:15">
       <c r="A336" s="1" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>36</v>
@@ -15954,10 +17192,10 @@
         <v>18</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>152</v>
@@ -15986,10 +17224,10 @@
     </row>
     <row r="337" spans="1:15">
       <c r="A337" s="1" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>80</v>
@@ -16001,7 +17239,7 @@
         <v>92</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>21</v>
@@ -16027,10 +17265,10 @@
     </row>
     <row r="338" spans="1:15">
       <c r="A338" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>36</v>
@@ -16039,10 +17277,10 @@
         <v>50</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G338" s="1" t="s">
         <v>21</v>
@@ -16065,10 +17303,10 @@
     </row>
     <row r="339" spans="1:15">
       <c r="A339" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>80</v>
@@ -16077,10 +17315,10 @@
         <v>18</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>23</v>
@@ -16106,10 +17344,10 @@
     </row>
     <row r="340" spans="1:15">
       <c r="A340" s="1" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>17</v>
@@ -16121,7 +17359,7 @@
         <v>59</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>47</v>
@@ -16147,10 +17385,10 @@
     </row>
     <row r="341" spans="1:15">
       <c r="A341" s="1" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>41</v>
@@ -16162,7 +17400,7 @@
         <v>42</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>44</v>
@@ -16182,10 +17420,10 @@
     </row>
     <row r="342" spans="1:15">
       <c r="A342" s="1" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>80</v>
@@ -16197,7 +17435,7 @@
         <v>37</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G342" s="1" t="s">
         <v>21</v>
@@ -16209,7 +17447,7 @@
         <v>26</v>
       </c>
       <c r="J342" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="O342" s="1" t="s">
         <v>29</v>
@@ -16217,10 +17455,10 @@
     </row>
     <row r="343" spans="1:15">
       <c r="A343" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>17</v>
@@ -16229,10 +17467,10 @@
         <v>18</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G343" s="1" t="s">
         <v>21</v>
@@ -16258,10 +17496,10 @@
     </row>
     <row r="344" spans="1:15">
       <c r="A344" s="1" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>41</v>
@@ -16273,7 +17511,7 @@
         <v>37</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>21</v>
@@ -16305,10 +17543,10 @@
     </row>
     <row r="345" spans="1:15">
       <c r="A345" s="1" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>80</v>
@@ -16320,7 +17558,7 @@
         <v>92</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>22</v>
@@ -16343,10 +17581,10 @@
     </row>
     <row r="346" spans="1:15">
       <c r="A346" s="1" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>17</v>
@@ -16358,7 +17596,7 @@
         <v>42</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G346" s="1" t="s">
         <v>44</v>
@@ -16381,10 +17619,10 @@
     </row>
     <row r="347" spans="1:15">
       <c r="A347" s="1" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>17</v>
@@ -16393,10 +17631,10 @@
         <v>18</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>22</v>
@@ -16425,10 +17663,10 @@
     </row>
     <row r="348" spans="1:15">
       <c r="A348" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>36</v>
@@ -16440,7 +17678,7 @@
         <v>59</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G348" s="1" t="s">
         <v>121</v>
@@ -16463,10 +17701,10 @@
     </row>
     <row r="349" spans="1:15">
       <c r="A349" s="1" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>36</v>
@@ -16475,10 +17713,10 @@
         <v>18</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G349" s="1" t="s">
         <v>21</v>
@@ -16510,10 +17748,10 @@
     </row>
     <row r="350" spans="1:15">
       <c r="A350" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>36</v>
@@ -16525,7 +17763,7 @@
         <v>92</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G350" s="1" t="s">
         <v>23</v>
@@ -16548,10 +17786,10 @@
     </row>
     <row r="351" spans="1:15">
       <c r="A351" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>80</v>
@@ -16563,13 +17801,13 @@
         <v>92</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G351" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H351" s="1" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>28</v>
@@ -16589,10 +17827,10 @@
     </row>
     <row r="352" spans="1:15">
       <c r="A352" s="1" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>36</v>
@@ -16601,10 +17839,10 @@
         <v>18</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G352" s="1" t="s">
         <v>21</v>
@@ -16630,10 +17868,10 @@
     </row>
     <row r="353" spans="1:15">
       <c r="A353" s="1" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>41</v>
@@ -16642,10 +17880,10 @@
         <v>50</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G353" s="1" t="s">
         <v>60</v>
@@ -16665,10 +17903,10 @@
     </row>
     <row r="354" spans="1:15">
       <c r="A354" s="1" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>36</v>
@@ -16677,10 +17915,10 @@
         <v>50</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G354" s="1" t="s">
         <v>21</v>
@@ -16706,10 +17944,10 @@
     </row>
     <row r="355" spans="1:15">
       <c r="A355" s="1" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>36</v>
@@ -16721,7 +17959,7 @@
         <v>37</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G355" s="1" t="s">
         <v>21</v>
@@ -16744,10 +17982,10 @@
     </row>
     <row r="356" spans="1:15">
       <c r="A356" s="1" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>36</v>
@@ -16756,10 +17994,10 @@
         <v>58</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G356" s="1" t="s">
         <v>21</v>
@@ -16785,10 +18023,10 @@
     </row>
     <row r="357" spans="1:15">
       <c r="A357" s="1" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>17</v>
@@ -16800,7 +18038,7 @@
         <v>37</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G357" s="1" t="s">
         <v>21</v>
@@ -16829,10 +18067,10 @@
     </row>
     <row r="358" spans="1:15">
       <c r="A358" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>80</v>
@@ -16841,10 +18079,10 @@
         <v>50</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G358" s="1" t="s">
         <v>21</v>
@@ -16873,10 +18111,10 @@
     </row>
     <row r="359" spans="1:15">
       <c r="A359" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>41</v>
@@ -16885,10 +18123,10 @@
         <v>58</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G359" s="1" t="s">
         <v>124</v>
@@ -16914,10 +18152,10 @@
     </row>
     <row r="360" spans="1:15">
       <c r="A360" s="1" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>36</v>
@@ -16929,7 +18167,7 @@
         <v>42</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G360" s="1" t="s">
         <v>44</v>
@@ -16952,10 +18190,10 @@
     </row>
     <row r="361" spans="1:15">
       <c r="A361" s="1" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>36</v>
@@ -16967,7 +18205,7 @@
         <v>37</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G361" s="1" t="s">
         <v>21</v>
@@ -16996,10 +18234,10 @@
     </row>
     <row r="362" spans="1:15">
       <c r="A362" s="1" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>36</v>
@@ -17011,7 +18249,7 @@
         <v>37</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G362" s="1" t="s">
         <v>21</v>
@@ -17040,10 +18278,10 @@
     </row>
     <row r="363" spans="1:15">
       <c r="A363" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>36</v>
@@ -17052,10 +18290,10 @@
         <v>18</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G363" s="1" t="s">
         <v>22</v>
@@ -17081,10 +18319,10 @@
     </row>
     <row r="364" spans="1:15">
       <c r="A364" s="1" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>17</v>
@@ -17093,10 +18331,10 @@
         <v>18</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G364" s="1" t="s">
         <v>23</v>
@@ -17125,10 +18363,10 @@
     </row>
     <row r="365" spans="1:15">
       <c r="A365" s="1" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>36</v>
@@ -17137,10 +18375,10 @@
         <v>50</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G365" s="1" t="s">
         <v>21</v>
@@ -17163,10 +18401,10 @@
     </row>
     <row r="366" spans="1:15">
       <c r="A366" s="1" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>80</v>
@@ -17178,7 +18416,7 @@
         <v>92</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>21</v>
@@ -17204,10 +18442,10 @@
     </row>
     <row r="367" spans="1:15">
       <c r="A367" s="1" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>17</v>
@@ -17219,7 +18457,7 @@
         <v>42</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>44</v>
@@ -17239,10 +18477,10 @@
     </row>
     <row r="368" spans="1:15">
       <c r="A368" s="1" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>36</v>
@@ -17254,7 +18492,7 @@
         <v>59</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>21</v>
@@ -17272,7 +18510,7 @@
         <v>33</v>
       </c>
       <c r="L368" s="1" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="O368" s="1" t="s">
         <v>29</v>
@@ -17280,10 +18518,10 @@
     </row>
     <row r="369" spans="1:15">
       <c r="A369" s="1" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>36</v>
@@ -17295,7 +18533,7 @@
         <v>42</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G369" s="1" t="s">
         <v>44</v>
@@ -17315,10 +18553,10 @@
     </row>
     <row r="370" spans="1:15">
       <c r="A370" s="1" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>80</v>
@@ -17330,7 +18568,7 @@
         <v>37</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G370" s="1" t="s">
         <v>21</v>
@@ -17350,10 +18588,10 @@
     </row>
     <row r="371" spans="1:15">
       <c r="A371" s="1" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>36</v>
@@ -17365,7 +18603,7 @@
         <v>37</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G371" s="1" t="s">
         <v>21</v>
@@ -17391,10 +18629,10 @@
     </row>
     <row r="372" spans="1:15">
       <c r="A372" s="1" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>41</v>
@@ -17403,10 +18641,10 @@
         <v>18</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G372" s="1" t="s">
         <v>21</v>
@@ -17429,10 +18667,10 @@
     </row>
     <row r="373" spans="1:15">
       <c r="A373" s="3" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>36</v>
@@ -17444,7 +18682,7 @@
         <v>37</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G373" s="1" t="s">
         <v>21</v>
@@ -17473,10 +18711,10 @@
     </row>
     <row r="374" spans="1:15">
       <c r="A374" s="1" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>36</v>
@@ -17485,10 +18723,10 @@
         <v>18</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>22</v>
@@ -17514,10 +18752,10 @@
     </row>
     <row r="375" spans="1:15">
       <c r="A375" s="1" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>36</v>
@@ -17529,7 +18767,7 @@
         <v>37</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G375" s="1" t="s">
         <v>84</v>
@@ -17549,10 +18787,10 @@
     </row>
     <row r="376" spans="1:15">
       <c r="A376" s="1" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>41</v>
@@ -17564,7 +18802,7 @@
         <v>92</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>22</v>
@@ -17584,10 +18822,10 @@
     </row>
     <row r="377" spans="1:15">
       <c r="A377" s="1" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>36</v>
@@ -17596,10 +18834,10 @@
         <v>58</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>21</v>
@@ -17628,10 +18866,10 @@
     </row>
     <row r="378" spans="1:15">
       <c r="A378" s="1" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>36</v>
@@ -17640,10 +18878,10 @@
         <v>18</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>21</v>
@@ -17672,10 +18910,10 @@
     </row>
     <row r="379" spans="1:15">
       <c r="A379" s="1" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>36</v>
@@ -17687,7 +18925,7 @@
         <v>37</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G379" s="1" t="s">
         <v>21</v>
@@ -17707,10 +18945,10 @@
     </row>
     <row r="380" spans="1:15">
       <c r="A380" s="1" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>17</v>
@@ -17722,7 +18960,7 @@
         <v>37</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G380" s="1" t="s">
         <v>21</v>
@@ -17748,10 +18986,10 @@
     </row>
     <row r="381" spans="1:15">
       <c r="A381" s="1" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>36</v>
@@ -17760,10 +18998,10 @@
         <v>18</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>23</v>
@@ -17792,10 +19030,10 @@
     </row>
     <row r="382" spans="1:15">
       <c r="A382" s="1" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>80</v>
@@ -17807,7 +19045,7 @@
         <v>92</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G382" s="1" t="s">
         <v>21</v>
@@ -17833,10 +19071,10 @@
     </row>
     <row r="383" spans="1:15">
       <c r="A383" s="1" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>36</v>
@@ -17848,7 +19086,7 @@
         <v>37</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G383" s="1" t="s">
         <v>21</v>
@@ -17874,10 +19112,10 @@
     </row>
     <row r="384" spans="1:15">
       <c r="A384" s="1" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>17</v>
@@ -17886,10 +19124,10 @@
         <v>18</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G384" s="1" t="s">
         <v>84</v>
@@ -17912,10 +19150,10 @@
     </row>
     <row r="385" spans="1:15">
       <c r="A385" s="1" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>36</v>
@@ -17924,10 +19162,10 @@
         <v>18</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>152</v>
@@ -17959,10 +19197,10 @@
     </row>
     <row r="386" spans="1:15">
       <c r="A386" s="1" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>36</v>
@@ -17974,7 +19212,7 @@
         <v>37</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G386" s="1" t="s">
         <v>21</v>
@@ -17994,10 +19232,10 @@
     </row>
     <row r="387" spans="1:15">
       <c r="A387" s="1" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>36</v>
@@ -18006,10 +19244,10 @@
         <v>58</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G387" s="1" t="s">
         <v>22</v>
@@ -18032,10 +19270,10 @@
     </row>
     <row r="388" spans="1:15">
       <c r="A388" s="1" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>41</v>
@@ -18047,7 +19285,7 @@
         <v>42</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>44</v>
@@ -18076,10 +19314,10 @@
     </row>
     <row r="389" spans="1:15">
       <c r="A389" s="1" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>80</v>
@@ -18091,7 +19329,7 @@
         <v>92</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G389" s="1" t="s">
         <v>21</v>
@@ -18117,10 +19355,10 @@
     </row>
     <row r="390" spans="1:15">
       <c r="A390" s="1" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>36</v>
@@ -18132,7 +19370,7 @@
         <v>37</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G390" s="1" t="s">
         <v>21</v>
@@ -18158,10 +19396,10 @@
     </row>
     <row r="391" spans="1:15">
       <c r="A391" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>17</v>
@@ -18170,10 +19408,10 @@
         <v>50</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>84</v>
@@ -18196,10 +19434,10 @@
     </row>
     <row r="392" spans="1:15">
       <c r="A392" s="1" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>80</v>
@@ -18211,7 +19449,7 @@
         <v>92</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>44</v>
@@ -18240,10 +19478,10 @@
     </row>
     <row r="393" spans="1:15">
       <c r="A393" s="1" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>41</v>
@@ -18255,7 +19493,7 @@
         <v>92</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>22</v>
@@ -18284,10 +19522,10 @@
     </row>
     <row r="394" spans="1:15">
       <c r="A394" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>36</v>
@@ -18299,7 +19537,7 @@
         <v>42</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>44</v>
@@ -18328,10 +19566,10 @@
     </row>
     <row r="395" spans="1:15">
       <c r="A395" s="1" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>17</v>
@@ -18343,7 +19581,7 @@
         <v>92</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G395" s="1" t="s">
         <v>21</v>
@@ -18366,10 +19604,10 @@
     </row>
     <row r="396" spans="1:15">
       <c r="A396" s="1" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>41</v>
@@ -18381,7 +19619,7 @@
         <v>37</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G396" s="1" t="s">
         <v>21</v>
@@ -18404,10 +19642,10 @@
     </row>
     <row r="397" spans="1:15">
       <c r="A397" s="3" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>41</v>
@@ -18419,7 +19657,7 @@
         <v>92</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G397" s="1" t="s">
         <v>21</v>
@@ -18445,10 +19683,10 @@
     </row>
     <row r="398" spans="1:15">
       <c r="A398" s="1" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>41</v>
@@ -18457,10 +19695,10 @@
         <v>58</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>22</v>
@@ -18481,10 +19719,10 @@
         <v>68</v>
       </c>
       <c r="M398" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="N398" s="1" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="O398" s="1" t="s">
         <v>29</v>
@@ -18492,10 +19730,10 @@
     </row>
     <row r="399" spans="1:15">
       <c r="A399" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>17</v>
@@ -18504,10 +19742,10 @@
         <v>50</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>21</v>
@@ -18530,10 +19768,10 @@
     </row>
     <row r="400" spans="1:15">
       <c r="A400" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>80</v>
@@ -18545,7 +19783,7 @@
         <v>59</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>121</v>
@@ -18568,10 +19806,10 @@
     </row>
     <row r="401" spans="1:15">
       <c r="A401" s="1" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>80</v>
@@ -18583,7 +19821,7 @@
         <v>92</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>60</v>

--- a/Data Cleaning/tickets_clean_400.xlsx
+++ b/Data Cleaning/tickets_clean_400.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="339" documentId="8_{5394F09E-6E80-4F68-9F58-63ABE0F9EBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8399803C-02AC-43FD-97CE-6FA7AE2FFAFC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C44BDCF4-9AA5-4868-940B-4296CED796B4}"/>
+    <workbookView xWindow="5640" yWindow="2295" windowWidth="28800" windowHeight="15255" xr2:uid="{C44BDCF4-9AA5-4868-940B-4296CED796B4}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -3301,7 +3301,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3318,7 +3318,6 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -11823,10 +11822,10 @@
       <c r="D202" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E202" s="6" t="s">
+      <c r="E202" t="s">
         <v>71</v>
       </c>
-      <c r="F202" s="6" t="s">
+      <c r="F202" t="s">
         <v>20</v>
       </c>
       <c r="G202" s="1" t="s">
@@ -11861,10 +11860,10 @@
       <c r="D203" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E203" s="6" t="s">
+      <c r="E203" t="s">
         <v>66</v>
       </c>
-      <c r="F203" s="6" t="s">
+      <c r="F203" t="s">
         <v>87</v>
       </c>
       <c r="G203" s="1" t="s">
@@ -11896,10 +11895,10 @@
       <c r="D204" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E204" s="6" t="s">
+      <c r="E204" t="s">
         <v>19</v>
       </c>
-      <c r="F204" s="6" t="s">
+      <c r="F204" t="s">
         <v>20</v>
       </c>
       <c r="G204" s="1" t="s">
@@ -11937,10 +11936,10 @@
       <c r="D205" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E205" s="6" t="s">
+      <c r="E205" t="s">
         <v>92</v>
       </c>
-      <c r="F205" s="6" t="s">
+      <c r="F205" t="s">
         <v>20</v>
       </c>
       <c r="G205" s="1" t="s">
@@ -11975,10 +11974,10 @@
       <c r="D206" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E206" s="6" t="s">
+      <c r="E206" t="s">
         <v>19</v>
       </c>
-      <c r="F206" s="6" t="s">
+      <c r="F206" t="s">
         <v>20</v>
       </c>
       <c r="G206" s="1" t="s">
@@ -12013,10 +12012,10 @@
       <c r="D207" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E207" s="6" t="s">
+      <c r="E207" t="s">
         <v>42</v>
       </c>
-      <c r="F207" s="6" t="s">
+      <c r="F207" t="s">
         <v>20</v>
       </c>
       <c r="G207" s="1" t="s">
@@ -12048,10 +12047,10 @@
       <c r="D208" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E208" s="6" t="s">
+      <c r="E208" t="s">
         <v>42</v>
       </c>
-      <c r="F208" s="6" t="s">
+      <c r="F208" t="s">
         <v>20</v>
       </c>
       <c r="G208" s="1" t="s">
@@ -12083,10 +12082,10 @@
       <c r="D209" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E209" s="6" t="s">
+      <c r="E209" t="s">
         <v>37</v>
       </c>
-      <c r="F209" s="6" t="s">
+      <c r="F209" t="s">
         <v>20</v>
       </c>
       <c r="G209" s="1" t="s">
@@ -12121,10 +12120,10 @@
       <c r="D210" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E210" s="6" t="s">
+      <c r="E210" t="s">
         <v>71</v>
       </c>
-      <c r="F210" s="6" t="s">
+      <c r="F210" t="s">
         <v>20</v>
       </c>
       <c r="G210" s="1" t="s">
@@ -12162,10 +12161,10 @@
       <c r="D211" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E211" s="6" t="s">
+      <c r="E211" t="s">
         <v>37</v>
       </c>
-      <c r="F211" s="6" t="s">
+      <c r="F211" t="s">
         <v>20</v>
       </c>
       <c r="G211" s="1" t="s">
@@ -12203,10 +12202,10 @@
       <c r="D212" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E212" s="6" t="s">
+      <c r="E212" t="s">
         <v>37</v>
       </c>
-      <c r="F212" s="6" t="s">
+      <c r="F212" t="s">
         <v>20</v>
       </c>
       <c r="G212" s="1" t="s">
@@ -12244,10 +12243,10 @@
       <c r="D213" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E213" s="6" t="s">
+      <c r="E213" t="s">
         <v>19</v>
       </c>
-      <c r="F213" s="6" t="s">
+      <c r="F213" t="s">
         <v>87</v>
       </c>
       <c r="G213" s="1" t="s">
@@ -12291,10 +12290,10 @@
       <c r="D214" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E214" s="6" t="s">
+      <c r="E214" t="s">
         <v>37</v>
       </c>
-      <c r="F214" s="6" t="s">
+      <c r="F214" t="s">
         <v>20</v>
       </c>
       <c r="G214" s="1" t="s">
@@ -12329,10 +12328,10 @@
       <c r="D215" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E215" s="6" t="s">
+      <c r="E215" t="s">
         <v>37</v>
       </c>
-      <c r="F215" s="6" t="s">
+      <c r="F215" t="s">
         <v>20</v>
       </c>
       <c r="G215" s="1" t="s">
@@ -12370,10 +12369,10 @@
       <c r="D216" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E216" s="6" t="s">
+      <c r="E216" t="s">
         <v>19</v>
       </c>
-      <c r="F216" s="6" t="s">
+      <c r="F216" t="s">
         <v>20</v>
       </c>
       <c r="G216" s="1" t="s">
@@ -12417,10 +12416,10 @@
       <c r="D217" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E217" s="6" t="s">
+      <c r="E217" t="s">
         <v>37</v>
       </c>
-      <c r="F217" s="6" t="s">
+      <c r="F217" t="s">
         <v>20</v>
       </c>
       <c r="G217" s="1" t="s">
@@ -12458,10 +12457,10 @@
       <c r="D218" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E218" s="6" t="s">
+      <c r="E218" t="s">
         <v>19</v>
       </c>
-      <c r="F218" s="6" t="s">
+      <c r="F218" t="s">
         <v>20</v>
       </c>
       <c r="G218" s="1" t="s">
@@ -12502,10 +12501,10 @@
       <c r="D219" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E219" s="6" t="s">
+      <c r="E219" t="s">
         <v>19</v>
       </c>
-      <c r="F219" s="6" t="s">
+      <c r="F219" t="s">
         <v>20</v>
       </c>
       <c r="G219" s="1" t="s">
@@ -12546,10 +12545,10 @@
       <c r="D220" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E220" s="6" t="s">
+      <c r="E220" t="s">
         <v>19</v>
       </c>
-      <c r="F220" s="6" t="s">
+      <c r="F220" t="s">
         <v>87</v>
       </c>
       <c r="G220" s="1" t="s">
@@ -12581,10 +12580,10 @@
       <c r="D221" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E221" s="6" t="s">
+      <c r="E221" t="s">
         <v>42</v>
       </c>
-      <c r="F221" s="6" t="s">
+      <c r="F221" t="s">
         <v>20</v>
       </c>
       <c r="G221" s="1" t="s">
@@ -12619,10 +12618,10 @@
       <c r="D222" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E222" s="6" t="s">
+      <c r="E222" t="s">
         <v>19</v>
       </c>
-      <c r="F222" s="6" t="s">
+      <c r="F222" t="s">
         <v>20</v>
       </c>
       <c r="G222" s="1" t="s">
@@ -12660,10 +12659,10 @@
       <c r="D223" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E223" s="6" t="s">
+      <c r="E223" t="s">
         <v>66</v>
       </c>
-      <c r="F223" s="6" t="s">
+      <c r="F223" t="s">
         <v>87</v>
       </c>
       <c r="G223" s="1" t="s">
@@ -12707,10 +12706,10 @@
       <c r="D224" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E224" s="6" t="s">
+      <c r="E224" t="s">
         <v>92</v>
       </c>
-      <c r="F224" s="6" t="s">
+      <c r="F224" t="s">
         <v>87</v>
       </c>
       <c r="G224" s="1" t="s">
@@ -12742,10 +12741,10 @@
       <c r="D225" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E225" s="6" t="s">
+      <c r="E225" t="s">
         <v>19</v>
       </c>
-      <c r="F225" s="6" t="s">
+      <c r="F225" t="s">
         <v>20</v>
       </c>
       <c r="G225" s="1" t="s">
@@ -12783,10 +12782,10 @@
       <c r="D226" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E226" s="6" t="s">
+      <c r="E226" t="s">
         <v>37</v>
       </c>
-      <c r="F226" s="6" t="s">
+      <c r="F226" t="s">
         <v>20</v>
       </c>
       <c r="G226" s="1" t="s">
@@ -12824,10 +12823,10 @@
       <c r="D227" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E227" s="6" t="s">
+      <c r="E227" t="s">
         <v>37</v>
       </c>
-      <c r="F227" s="6" t="s">
+      <c r="F227" t="s">
         <v>20</v>
       </c>
       <c r="G227" s="1" t="s">
@@ -12862,10 +12861,10 @@
       <c r="D228" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E228" s="6" t="s">
+      <c r="E228" t="s">
         <v>37</v>
       </c>
-      <c r="F228" s="6" t="s">
+      <c r="F228" t="s">
         <v>20</v>
       </c>
       <c r="G228" s="1" t="s">
@@ -12897,10 +12896,10 @@
       <c r="D229" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E229" s="6" t="s">
+      <c r="E229" t="s">
         <v>19</v>
       </c>
-      <c r="F229" s="6" t="s">
+      <c r="F229" t="s">
         <v>20</v>
       </c>
       <c r="G229" s="1" t="s">
@@ -12944,10 +12943,10 @@
       <c r="D230" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E230" s="6" t="s">
+      <c r="E230" t="s">
         <v>37</v>
       </c>
-      <c r="F230" s="6" t="s">
+      <c r="F230" t="s">
         <v>20</v>
       </c>
       <c r="G230" s="1" t="s">
@@ -12985,10 +12984,10 @@
       <c r="D231" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E231" s="6" t="s">
+      <c r="E231" t="s">
         <v>19</v>
       </c>
-      <c r="F231" s="6" t="s">
+      <c r="F231" t="s">
         <v>20</v>
       </c>
       <c r="G231" s="1" t="s">
@@ -13026,10 +13025,10 @@
       <c r="D232" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E232" s="6" t="s">
+      <c r="E232" t="s">
         <v>37</v>
       </c>
-      <c r="F232" s="6" t="s">
+      <c r="F232" t="s">
         <v>20</v>
       </c>
       <c r="G232" s="1" t="s">
@@ -13064,10 +13063,10 @@
       <c r="D233" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E233" s="6" t="s">
+      <c r="E233" t="s">
         <v>37</v>
       </c>
-      <c r="F233" s="6" t="s">
+      <c r="F233" t="s">
         <v>20</v>
       </c>
       <c r="G233" s="1" t="s">
@@ -13099,10 +13098,10 @@
       <c r="D234" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E234" s="6" t="s">
+      <c r="E234" t="s">
         <v>37</v>
       </c>
-      <c r="F234" s="6" t="s">
+      <c r="F234" t="s">
         <v>20</v>
       </c>
       <c r="G234" s="1" t="s">
@@ -13137,10 +13136,10 @@
       <c r="D235" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E235" s="6" t="s">
+      <c r="E235" t="s">
         <v>19</v>
       </c>
-      <c r="F235" s="6" t="s">
+      <c r="F235" t="s">
         <v>20</v>
       </c>
       <c r="G235" s="1" t="s">
@@ -13175,10 +13174,10 @@
       <c r="D236" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E236" s="6" t="s">
+      <c r="E236" t="s">
         <v>66</v>
       </c>
-      <c r="F236" s="6" t="s">
+      <c r="F236" t="s">
         <v>20</v>
       </c>
       <c r="G236" s="1" t="s">
@@ -13219,10 +13218,10 @@
       <c r="D237" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E237" s="6" t="s">
+      <c r="E237" t="s">
         <v>19</v>
       </c>
-      <c r="F237" s="6" t="s">
+      <c r="F237" t="s">
         <v>20</v>
       </c>
       <c r="G237" s="1" t="s">
@@ -13263,10 +13262,10 @@
       <c r="D238" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E238" s="6" t="s">
+      <c r="E238" t="s">
         <v>19</v>
       </c>
-      <c r="F238" s="6" t="s">
+      <c r="F238" t="s">
         <v>20</v>
       </c>
       <c r="G238" s="1" t="s">
@@ -13301,10 +13300,10 @@
       <c r="D239" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E239" s="6" t="s">
+      <c r="E239" t="s">
         <v>42</v>
       </c>
-      <c r="F239" s="6" t="s">
+      <c r="F239" t="s">
         <v>20</v>
       </c>
       <c r="G239" s="1" t="s">
@@ -13339,10 +13338,10 @@
       <c r="D240" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E240" s="6" t="s">
+      <c r="E240" t="s">
         <v>59</v>
       </c>
-      <c r="F240" s="6" t="s">
+      <c r="F240" t="s">
         <v>20</v>
       </c>
       <c r="G240" s="1" t="s">
@@ -13377,10 +13376,10 @@
       <c r="D241" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E241" s="6" t="s">
+      <c r="E241" t="s">
         <v>19</v>
       </c>
-      <c r="F241" s="6" t="s">
+      <c r="F241" t="s">
         <v>20</v>
       </c>
       <c r="G241" s="1" t="s">
@@ -13421,10 +13420,10 @@
       <c r="D242" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E242" s="6" t="s">
+      <c r="E242" t="s">
         <v>37</v>
       </c>
-      <c r="F242" s="6" t="s">
+      <c r="F242" t="s">
         <v>20</v>
       </c>
       <c r="G242" s="1" t="s">
@@ -13465,10 +13464,10 @@
       <c r="D243" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E243" s="6" t="s">
+      <c r="E243" t="s">
         <v>37</v>
       </c>
-      <c r="F243" s="6" t="s">
+      <c r="F243" t="s">
         <v>20</v>
       </c>
       <c r="G243" s="1" t="s">
@@ -13500,10 +13499,10 @@
       <c r="D244" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E244" s="6" t="s">
+      <c r="E244" t="s">
         <v>19</v>
       </c>
-      <c r="F244" s="6" t="s">
+      <c r="F244" t="s">
         <v>20</v>
       </c>
       <c r="G244" s="1" t="s">
@@ -13541,10 +13540,10 @@
       <c r="D245" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E245" s="6" t="s">
+      <c r="E245" t="s">
         <v>19</v>
       </c>
-      <c r="F245" s="6" t="s">
+      <c r="F245" t="s">
         <v>20</v>
       </c>
       <c r="G245" s="1" t="s">
@@ -13582,10 +13581,10 @@
       <c r="D246" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E246" s="6" t="s">
+      <c r="E246" t="s">
         <v>19</v>
       </c>
-      <c r="F246" s="6" t="s">
+      <c r="F246" t="s">
         <v>20</v>
       </c>
       <c r="G246" s="1" t="s">
@@ -13629,10 +13628,10 @@
       <c r="D247" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E247" s="6" t="s">
+      <c r="E247" t="s">
         <v>19</v>
       </c>
-      <c r="F247" s="6" t="s">
+      <c r="F247" t="s">
         <v>20</v>
       </c>
       <c r="G247" s="1" t="s">
@@ -13673,10 +13672,10 @@
       <c r="D248" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E248" s="6" t="s">
+      <c r="E248" t="s">
         <v>42</v>
       </c>
-      <c r="F248" s="6" t="s">
+      <c r="F248" t="s">
         <v>20</v>
       </c>
       <c r="G248" s="1" t="s">
@@ -13717,10 +13716,10 @@
       <c r="D249" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E249" s="6" t="s">
+      <c r="E249" t="s">
         <v>37</v>
       </c>
-      <c r="F249" s="6" t="s">
+      <c r="F249" t="s">
         <v>20</v>
       </c>
       <c r="G249" s="1" t="s">
@@ -13764,10 +13763,10 @@
       <c r="D250" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E250" s="6" t="s">
+      <c r="E250" t="s">
         <v>71</v>
       </c>
-      <c r="F250" s="6" t="s">
+      <c r="F250" t="s">
         <v>20</v>
       </c>
       <c r="G250" s="1" t="s">
@@ -13805,10 +13804,10 @@
       <c r="D251" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E251" s="6" t="s">
+      <c r="E251" t="s">
         <v>37</v>
       </c>
-      <c r="F251" s="6" t="s">
+      <c r="F251" t="s">
         <v>20</v>
       </c>
       <c r="G251" s="1" t="s">
@@ -13846,10 +13845,10 @@
       <c r="D252" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E252" s="6" t="s">
+      <c r="E252" t="s">
         <v>19</v>
       </c>
-      <c r="F252" s="6" t="s">
+      <c r="F252" t="s">
         <v>20</v>
       </c>
       <c r="G252" s="1" t="s">
@@ -13884,10 +13883,10 @@
       <c r="D253" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E253" s="6" t="s">
+      <c r="E253" t="s">
         <v>37</v>
       </c>
-      <c r="F253" s="6" t="s">
+      <c r="F253" t="s">
         <v>20</v>
       </c>
       <c r="G253" s="1" t="s">
@@ -13922,10 +13921,10 @@
       <c r="D254" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E254" s="6" t="s">
+      <c r="E254" t="s">
         <v>66</v>
       </c>
-      <c r="F254" s="6" t="s">
+      <c r="F254" t="s">
         <v>87</v>
       </c>
       <c r="G254" s="1" t="s">
@@ -13963,10 +13962,10 @@
       <c r="D255" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E255" s="6" t="s">
+      <c r="E255" t="s">
         <v>37</v>
       </c>
-      <c r="F255" s="6" t="s">
+      <c r="F255" t="s">
         <v>20</v>
       </c>
       <c r="G255" s="1" t="s">
@@ -14004,10 +14003,10 @@
       <c r="D256" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E256" s="6" t="s">
+      <c r="E256" t="s">
         <v>37</v>
       </c>
-      <c r="F256" s="6" t="s">
+      <c r="F256" t="s">
         <v>20</v>
       </c>
       <c r="G256" s="1" t="s">
@@ -14042,10 +14041,10 @@
       <c r="D257" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E257" s="6" t="s">
+      <c r="E257" t="s">
         <v>37</v>
       </c>
-      <c r="F257" s="6" t="s">
+      <c r="F257" t="s">
         <v>20</v>
       </c>
       <c r="G257" s="1" t="s">
@@ -14080,10 +14079,10 @@
       <c r="D258" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E258" s="6" t="s">
+      <c r="E258" t="s">
         <v>37</v>
       </c>
-      <c r="F258" s="6" t="s">
+      <c r="F258" t="s">
         <v>20</v>
       </c>
       <c r="G258" s="1" t="s">
@@ -14118,10 +14117,10 @@
       <c r="D259" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E259" s="6" t="s">
+      <c r="E259" t="s">
         <v>19</v>
       </c>
-      <c r="F259" s="6" t="s">
+      <c r="F259" t="s">
         <v>20</v>
       </c>
       <c r="G259" s="1" t="s">
@@ -14159,10 +14158,10 @@
       <c r="D260" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E260" s="6" t="s">
+      <c r="E260" t="s">
         <v>37</v>
       </c>
-      <c r="F260" s="6" t="s">
+      <c r="F260" t="s">
         <v>20</v>
       </c>
       <c r="G260" s="1" t="s">
@@ -14200,10 +14199,10 @@
       <c r="D261" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E261" s="6" t="s">
+      <c r="E261" t="s">
         <v>71</v>
       </c>
-      <c r="F261" s="6" t="s">
+      <c r="F261" t="s">
         <v>20</v>
       </c>
       <c r="G261" s="1" t="s">
@@ -14235,10 +14234,10 @@
       <c r="D262" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E262" s="6" t="s">
+      <c r="E262" t="s">
         <v>19</v>
       </c>
-      <c r="F262" s="6" t="s">
+      <c r="F262" t="s">
         <v>87</v>
       </c>
       <c r="G262" s="1" t="s">
@@ -14276,10 +14275,10 @@
       <c r="D263" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E263" s="6" t="s">
+      <c r="E263" t="s">
         <v>59</v>
       </c>
-      <c r="F263" s="6" t="s">
+      <c r="F263" t="s">
         <v>20</v>
       </c>
       <c r="G263" s="1" t="s">
@@ -14314,10 +14313,10 @@
       <c r="D264" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E264" s="6" t="s">
+      <c r="E264" t="s">
         <v>37</v>
       </c>
-      <c r="F264" s="6" t="s">
+      <c r="F264" t="s">
         <v>20</v>
       </c>
       <c r="G264" s="1" t="s">
@@ -14352,10 +14351,10 @@
       <c r="D265" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E265" s="6" t="s">
+      <c r="E265" t="s">
         <v>92</v>
       </c>
-      <c r="F265" s="6" t="s">
+      <c r="F265" t="s">
         <v>20</v>
       </c>
       <c r="G265" s="1" t="s">
@@ -14387,10 +14386,10 @@
       <c r="D266" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E266" s="6" t="s">
+      <c r="E266" t="s">
         <v>37</v>
       </c>
-      <c r="F266" s="6" t="s">
+      <c r="F266" t="s">
         <v>20</v>
       </c>
       <c r="G266" s="1" t="s">
@@ -14425,10 +14424,10 @@
       <c r="D267" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E267" s="6" t="s">
+      <c r="E267" t="s">
         <v>19</v>
       </c>
-      <c r="F267" s="6" t="s">
+      <c r="F267" t="s">
         <v>20</v>
       </c>
       <c r="G267" s="1" t="s">
@@ -14472,10 +14471,10 @@
       <c r="D268" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E268" s="6" t="s">
+      <c r="E268" t="s">
         <v>19</v>
       </c>
-      <c r="F268" s="6" t="s">
+      <c r="F268" t="s">
         <v>20</v>
       </c>
       <c r="G268" s="1" t="s">
@@ -14513,10 +14512,10 @@
       <c r="D269" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E269" s="6" t="s">
+      <c r="E269" t="s">
         <v>66</v>
       </c>
-      <c r="F269" s="6" t="s">
+      <c r="F269" t="s">
         <v>87</v>
       </c>
       <c r="G269" s="1" t="s">
@@ -14560,10 +14559,10 @@
       <c r="D270" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E270" s="6" t="s">
+      <c r="E270" t="s">
         <v>42</v>
       </c>
-      <c r="F270" s="6" t="s">
+      <c r="F270" t="s">
         <v>20</v>
       </c>
       <c r="G270" s="1" t="s">
@@ -14598,10 +14597,10 @@
       <c r="D271" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E271" s="6" t="s">
+      <c r="E271" t="s">
         <v>19</v>
       </c>
-      <c r="F271" s="6" t="s">
+      <c r="F271" t="s">
         <v>20</v>
       </c>
       <c r="G271" s="1" t="s">
@@ -14642,10 +14641,10 @@
       <c r="D272" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E272" s="6" t="s">
+      <c r="E272" t="s">
         <v>37</v>
       </c>
-      <c r="F272" s="6" t="s">
+      <c r="F272" t="s">
         <v>20</v>
       </c>
       <c r="G272" s="1" t="s">
@@ -14689,10 +14688,10 @@
       <c r="D273" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E273" s="6" t="s">
+      <c r="E273" t="s">
         <v>19</v>
       </c>
-      <c r="F273" s="6" t="s">
+      <c r="F273" t="s">
         <v>20</v>
       </c>
       <c r="G273" s="1" t="s">
@@ -14730,10 +14729,10 @@
       <c r="D274" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E274" s="6" t="s">
+      <c r="E274" t="s">
         <v>37</v>
       </c>
-      <c r="F274" s="6" t="s">
+      <c r="F274" t="s">
         <v>20</v>
       </c>
       <c r="G274" s="1" t="s">
@@ -14765,10 +14764,10 @@
       <c r="D275" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E275" s="6" t="s">
+      <c r="E275" t="s">
         <v>66</v>
       </c>
-      <c r="F275" s="6" t="s">
+      <c r="F275" t="s">
         <v>87</v>
       </c>
       <c r="G275" s="1" t="s">
@@ -14809,10 +14808,10 @@
       <c r="D276" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E276" s="6" t="s">
+      <c r="E276" t="s">
         <v>59</v>
       </c>
-      <c r="F276" s="6" t="s">
+      <c r="F276" t="s">
         <v>20</v>
       </c>
       <c r="G276" s="1" t="s">
@@ -14847,10 +14846,10 @@
       <c r="D277" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E277" s="6" t="s">
+      <c r="E277" t="s">
         <v>37</v>
       </c>
-      <c r="F277" s="6" t="s">
+      <c r="F277" t="s">
         <v>20</v>
       </c>
       <c r="G277" s="1" t="s">
@@ -14894,10 +14893,10 @@
       <c r="D278" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E278" s="6" t="s">
+      <c r="E278" t="s">
         <v>37</v>
       </c>
-      <c r="F278" s="6" t="s">
+      <c r="F278" t="s">
         <v>20</v>
       </c>
       <c r="G278" s="1" t="s">
@@ -14932,10 +14931,10 @@
       <c r="D279" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E279" s="6" t="s">
+      <c r="E279" t="s">
         <v>19</v>
       </c>
-      <c r="F279" s="6" t="s">
+      <c r="F279" t="s">
         <v>20</v>
       </c>
       <c r="G279" s="1" t="s">
@@ -14970,10 +14969,10 @@
       <c r="D280" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E280" s="6" t="s">
+      <c r="E280" t="s">
         <v>59</v>
       </c>
-      <c r="F280" s="6" t="s">
+      <c r="F280" t="s">
         <v>20</v>
       </c>
       <c r="G280" s="1" t="s">
@@ -15008,10 +15007,10 @@
       <c r="D281" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E281" s="6" t="s">
+      <c r="E281" t="s">
         <v>59</v>
       </c>
-      <c r="F281" s="6" t="s">
+      <c r="F281" t="s">
         <v>20</v>
       </c>
       <c r="G281" s="1" t="s">
@@ -15049,10 +15048,10 @@
       <c r="D282" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E282" s="6" t="s">
+      <c r="E282" t="s">
         <v>71</v>
       </c>
-      <c r="F282" s="6" t="s">
+      <c r="F282" t="s">
         <v>20</v>
       </c>
       <c r="G282" s="1" t="s">
@@ -15087,10 +15086,10 @@
       <c r="D283" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E283" s="6" t="s">
+      <c r="E283" t="s">
         <v>19</v>
       </c>
-      <c r="F283" s="6" t="s">
+      <c r="F283" t="s">
         <v>20</v>
       </c>
       <c r="G283" s="1" t="s">
@@ -15125,10 +15124,10 @@
       <c r="D284" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E284" s="6" t="s">
+      <c r="E284" t="s">
         <v>19</v>
       </c>
-      <c r="F284" s="6" t="s">
+      <c r="F284" t="s">
         <v>20</v>
       </c>
       <c r="G284" s="1" t="s">
@@ -15169,10 +15168,10 @@
       <c r="D285" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E285" s="6" t="s">
+      <c r="E285" t="s">
         <v>19</v>
       </c>
-      <c r="F285" s="6" t="s">
+      <c r="F285" t="s">
         <v>20</v>
       </c>
       <c r="G285" s="1" t="s">
@@ -15213,10 +15212,10 @@
       <c r="D286" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E286" s="6" t="s">
+      <c r="E286" t="s">
         <v>59</v>
       </c>
-      <c r="F286" s="6" t="s">
+      <c r="F286" t="s">
         <v>20</v>
       </c>
       <c r="G286" s="1" t="s">
@@ -15254,10 +15253,10 @@
       <c r="D287" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E287" s="6" t="s">
+      <c r="E287" t="s">
         <v>19</v>
       </c>
-      <c r="F287" s="6" t="s">
+      <c r="F287" t="s">
         <v>20</v>
       </c>
       <c r="G287" s="1" t="s">
@@ -15298,10 +15297,10 @@
       <c r="D288" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E288" s="6" t="s">
+      <c r="E288" t="s">
         <v>37</v>
       </c>
-      <c r="F288" s="6" t="s">
+      <c r="F288" t="s">
         <v>20</v>
       </c>
       <c r="G288" s="1" t="s">
@@ -15336,10 +15335,10 @@
       <c r="D289" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E289" s="6" t="s">
+      <c r="E289" t="s">
         <v>19</v>
       </c>
-      <c r="F289" s="6" t="s">
+      <c r="F289" t="s">
         <v>20</v>
       </c>
       <c r="G289" s="1" t="s">
@@ -15377,10 +15376,10 @@
       <c r="D290" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E290" s="6" t="s">
+      <c r="E290" t="s">
         <v>42</v>
       </c>
-      <c r="F290" s="6" t="s">
+      <c r="F290" t="s">
         <v>20</v>
       </c>
       <c r="G290" s="1" t="s">
@@ -15418,10 +15417,10 @@
       <c r="D291" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E291" s="6" t="s">
+      <c r="E291" t="s">
         <v>71</v>
       </c>
-      <c r="F291" s="6" t="s">
+      <c r="F291" t="s">
         <v>87</v>
       </c>
       <c r="G291" s="1" t="s">
@@ -15459,10 +15458,10 @@
       <c r="D292" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E292" s="6" t="s">
+      <c r="E292" t="s">
         <v>19</v>
       </c>
-      <c r="F292" s="6" t="s">
+      <c r="F292" t="s">
         <v>20</v>
       </c>
       <c r="G292" s="1" t="s">
@@ -15500,10 +15499,10 @@
       <c r="D293" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E293" s="6" t="s">
+      <c r="E293" t="s">
         <v>37</v>
       </c>
-      <c r="F293" s="6" t="s">
+      <c r="F293" t="s">
         <v>20</v>
       </c>
       <c r="G293" s="1" t="s">
@@ -15538,10 +15537,10 @@
       <c r="D294" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E294" s="6" t="s">
+      <c r="E294" t="s">
         <v>66</v>
       </c>
-      <c r="F294" s="6" t="s">
+      <c r="F294" t="s">
         <v>87</v>
       </c>
       <c r="G294" s="1" t="s">
@@ -15573,10 +15572,10 @@
       <c r="D295" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E295" s="6" t="s">
+      <c r="E295" t="s">
         <v>19</v>
       </c>
-      <c r="F295" s="6" t="s">
+      <c r="F295" t="s">
         <v>20</v>
       </c>
       <c r="G295" s="1" t="s">
@@ -15620,10 +15619,10 @@
       <c r="D296" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E296" s="6" t="s">
+      <c r="E296" t="s">
         <v>19</v>
       </c>
-      <c r="F296" s="6" t="s">
+      <c r="F296" t="s">
         <v>20</v>
       </c>
       <c r="G296" s="1" t="s">
@@ -15658,10 +15657,10 @@
       <c r="D297" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E297" s="6" t="s">
+      <c r="E297" t="s">
         <v>71</v>
       </c>
-      <c r="F297" s="6" t="s">
+      <c r="F297" t="s">
         <v>20</v>
       </c>
       <c r="G297" s="1" t="s">
@@ -15696,10 +15695,10 @@
       <c r="D298" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E298" s="6" t="s">
+      <c r="E298" t="s">
         <v>19</v>
       </c>
-      <c r="F298" s="6" t="s">
+      <c r="F298" t="s">
         <v>20</v>
       </c>
       <c r="G298" s="1" t="s">
@@ -15743,10 +15742,10 @@
       <c r="D299" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E299" s="6" t="s">
+      <c r="E299" t="s">
         <v>71</v>
       </c>
-      <c r="F299" s="6" t="s">
+      <c r="F299" t="s">
         <v>87</v>
       </c>
       <c r="G299" s="1" t="s">
@@ -15781,10 +15780,10 @@
       <c r="D300" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E300" s="6" t="s">
+      <c r="E300" t="s">
         <v>19</v>
       </c>
-      <c r="F300" s="6" t="s">
+      <c r="F300" t="s">
         <v>20</v>
       </c>
       <c r="G300" s="1" t="s">
@@ -15822,10 +15821,10 @@
       <c r="D301" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E301" s="6" t="s">
+      <c r="E301" t="s">
         <v>37</v>
       </c>
-      <c r="F301" s="6" t="s">
+      <c r="F301" t="s">
         <v>20</v>
       </c>
       <c r="G301" s="1" t="s">
